--- a/templates/informe-cortesia.xlsx
+++ b/templates/informe-cortesia.xlsx
@@ -1870,7 +1870,7 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FFFF0000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>

--- a/templates/informe-cortesia.xlsx
+++ b/templates/informe-cortesia.xlsx
@@ -17835,15 +17835,6 @@
     <mergeCell ref="B4:H4"/>
     <mergeCell ref="B5:H5"/>
   </mergeCells>
-  <conditionalFormatting sqref="A4">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B7:B215">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B1:C1 A5 B216:C1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>

--- a/templates/informe-cortesia.xlsx
+++ b/templates/informe-cortesia.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10920"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliocontreras/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{554F5248-8249-7A47-A962-FAF61A32A083}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC20A7E4-2D1A-E742-8299-24595FB4FA58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="21600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="38400" windowHeight="19760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Inicio" sheetId="219" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <definedName name="valoracion">#REF!</definedName>
     <definedName name="ventas">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" calcOnSave="0"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -122,7 +122,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="986" uniqueCount="472">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="985" uniqueCount="473">
   <si>
     <t>FECHA:</t>
   </si>
@@ -1234,9 +1234,6 @@
   </si>
   <si>
     <t>Unidad Funcional</t>
-  </si>
-  <si>
-    <t>Muestra el flujo de caja promedio del trabajador llevado a la escala de un mes estándar de 30 días. Este cálculo consolida todos los pagos mensuales más la proyección de aquellos ingresos con frecuencias distintas (bimestrales, trimestrales, bonos por desempeño anuales, etc.), sumándolos en un monto anual que luego se divide entre 12. Al igual que el TEM, excluye estrictamente el impacto de las alícuotas de los pasivos laborales. Es ideal para medir el ingreso real disponible del trabajador en promedio.</t>
   </si>
   <si>
     <t>Compensación Integral Mensual (CIM)</t>
@@ -1595,6 +1592,12 @@
   </si>
   <si>
     <t>METODOLOGÍA</t>
+  </si>
+  <si>
+    <t>OCTUBRE 2026</t>
+  </si>
+  <si>
+    <t>Es el indicador del valor económico total del paquete retributivo expresado en fracciones mensuales. Integra el "Total Efectivo Mensualizado" y le suma el peso financiero (las alícuotas mensuales) de todos los pasivos laborales garantizados por ley o contrato, entiéndase: utilidades, bono vacacional y prestaciones sociales. Este cálculo permite a la empresa visualizar el impacto económico integral de la posición mes a mes, incluyendo las provisiones obligatorias.</t>
   </si>
 </sst>
 </file>
@@ -2555,6 +2558,64 @@
     <xf numFmtId="164" fontId="25" fillId="4" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="top" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection hidden="1"/>
@@ -2578,8 +2639,87 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="2" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="21" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2614,70 +2754,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="13" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="14" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="16" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="2" borderId="17" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="13" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="14" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="16" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="21" fillId="0" borderId="17" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2700,89 +2776,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection hidden="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right" vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="33" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" readingOrder="1"/>
-      <protection hidden="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment wrapText="1"/>
       <protection hidden="1"/>
     </xf>
   </cellXfs>
@@ -4211,54 +4214,6 @@
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>775608</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>193895</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 5" descr="Alamy_AAYK2P_PPT">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0C00-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:alphaModFix amt="50000"/>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1" y="1"/>
-          <a:ext cx="5652407" cy="2022694"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -4305,7 +4260,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -4364,7 +4319,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -4380,6 +4335,52 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>742327</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 5" descr="Alamy_AAYK2P_PPT">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04B297A8-90F6-F74A-B539-75A61AD14153}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5621244" cy="1989043"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -7785,311 +7786,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>304800</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Picture 5">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96EE4111-5C80-E746-B770-4E98577DFBA0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="27505" t="1430" r="27486" b="34187"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5678311" y="0"/>
-          <a:ext cx="292100" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>647700</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="Picture 5">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FF798B49-0CB6-964F-B389-62A54EDB4209}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:srcRect l="27505" t="1430" r="27486" b="34187"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="5678311" y="342900"/>
-          <a:ext cx="292100" cy="304800"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>450272</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>11546</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>804390</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>727363</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="5 CuadroTexto">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A53BA781-C48F-5546-953A-C8BC030886A9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5925383" y="11546"/>
-          <a:ext cx="1186674" cy="715817"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:txBody>
-        <a:bodyPr wrap="square" rtlCol="0">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle>
-          <a:defPPr>
-            <a:defRPr lang="es-VE"/>
-          </a:defPPr>
-          <a:lvl1pPr marL="0" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl1pPr>
-          <a:lvl2pPr marL="457200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl2pPr>
-          <a:lvl3pPr marL="914400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl3pPr>
-          <a:lvl4pPr marL="1371600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl4pPr>
-          <a:lvl5pPr marL="1828800" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl5pPr>
-          <a:lvl6pPr marL="2286000" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl6pPr>
-          <a:lvl7pPr marL="2743200" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl7pPr>
-          <a:lvl8pPr marL="3200400" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl8pPr>
-          <a:lvl9pPr marL="3657600" algn="l" defTabSz="914400" rtl="0" eaLnBrk="1" latinLnBrk="0" hangingPunct="1">
-            <a:defRPr sz="1800" kern="1200">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:lvl9pPr>
-        </a:lstStyle>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1100"/>
-            <a:t>@ac_consulting</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1100"/>
-            <a:t> </a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr lang="es-ES" sz="1100"/>
-            <a:t>@avgh_rrhh</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -8134,7 +7830,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -8193,7 +7889,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -8313,7 +8009,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -8391,7 +8087,7 @@
           </xdr:xfrm>
           <a:graphic>
             <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2014/chartex">
-              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
+              <cx:chart xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
             </a:graphicData>
           </a:graphic>
         </xdr:graphicFrame>
@@ -8453,7 +8149,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="20" name="Picture 5">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6073F189-B1D5-5740-AD1D-9A400BE90E96}"/>
@@ -8465,7 +8161,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -8528,7 +8224,7 @@
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="21" name="Picture 5">
-          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7"/>
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
               <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71716E2A-5B12-424E-8C5E-DFE83E3C4002}"/>
@@ -8540,7 +8236,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
               <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -8747,54 +8443,6 @@
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>775608</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>193895</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 5" descr="Alamy_AAYK2P_PPT">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0900-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:alphaModFix amt="50000"/>
-        </a:blip>
-        <a:srcRect/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
-        <a:xfrm>
-          <a:off x="1" y="1"/>
-          <a:ext cx="5652407" cy="2022694"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>2</xdr:col>
@@ -8841,7 +8489,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
             <a:extLst>
               <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
                 <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
@@ -8900,7 +8548,7 @@
           </xdr:cNvPicPr>
         </xdr:nvPicPr>
         <xdr:blipFill>
-          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
           <a:stretch>
             <a:fillRect/>
           </a:stretch>
@@ -8916,6 +8564,52 @@
         </xdr:spPr>
       </xdr:pic>
     </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>742327</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>179293</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 5" descr="Alamy_AAYK2P_PPT">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C48A7732-BCC9-D84F-8DD9-8F6F9CEB3942}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print"/>
+        <a:srcRect/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="0"/>
+          <a:ext cx="5621244" cy="1989043"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+    </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -10651,12 +10345,12 @@
   </cols>
   <sheetData>
     <row r="12" spans="1:6" ht="21" x14ac:dyDescent="0.25">
-      <c r="A12" s="98"/>
-      <c r="B12" s="98"/>
-      <c r="C12" s="98"/>
-      <c r="D12" s="98"/>
-      <c r="E12" s="98"/>
-      <c r="F12" s="98"/>
+      <c r="A12" s="113"/>
+      <c r="B12" s="113"/>
+      <c r="C12" s="113"/>
+      <c r="D12" s="113"/>
+      <c r="E12" s="113"/>
+      <c r="F12" s="113"/>
     </row>
     <row r="13" spans="1:6" ht="5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="36"/>
@@ -10816,10 +10510,10 @@
       <c r="L1" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="N1" s="133" t="s">
+      <c r="N1" s="152" t="s">
         <v>55</v>
       </c>
-      <c r="O1" s="133"/>
+      <c r="O1" s="152"/>
     </row>
     <row r="2" spans="2:15" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="14"/>
@@ -10838,238 +10532,238 @@
       <c r="G3" s="14"/>
     </row>
     <row r="4" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B4" s="131" t="s">
+      <c r="B4" s="150" t="s">
         <v>136</v>
       </c>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="151"/>
+      <c r="E4" s="151"/>
+      <c r="F4" s="151"/>
+      <c r="G4" s="151"/>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B5" s="132"/>
-      <c r="C5" s="132"/>
-      <c r="D5" s="132"/>
-      <c r="E5" s="132"/>
-      <c r="F5" s="132"/>
-      <c r="G5" s="132"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="151"/>
+      <c r="E5" s="151"/>
+      <c r="F5" s="151"/>
+      <c r="G5" s="151"/>
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B6" s="132"/>
-      <c r="C6" s="132"/>
-      <c r="D6" s="132"/>
-      <c r="E6" s="132"/>
-      <c r="F6" s="132"/>
-      <c r="G6" s="132"/>
+      <c r="B6" s="151"/>
+      <c r="C6" s="151"/>
+      <c r="D6" s="151"/>
+      <c r="E6" s="151"/>
+      <c r="F6" s="151"/>
+      <c r="G6" s="151"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B7" s="132"/>
-      <c r="C7" s="132"/>
-      <c r="D7" s="132"/>
-      <c r="E7" s="132"/>
-      <c r="F7" s="132"/>
-      <c r="G7" s="132"/>
+      <c r="B7" s="151"/>
+      <c r="C7" s="151"/>
+      <c r="D7" s="151"/>
+      <c r="E7" s="151"/>
+      <c r="F7" s="151"/>
+      <c r="G7" s="151"/>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B8" s="132"/>
-      <c r="C8" s="132"/>
-      <c r="D8" s="132"/>
-      <c r="E8" s="132"/>
-      <c r="F8" s="132"/>
-      <c r="G8" s="132"/>
+      <c r="B8" s="151"/>
+      <c r="C8" s="151"/>
+      <c r="D8" s="151"/>
+      <c r="E8" s="151"/>
+      <c r="F8" s="151"/>
+      <c r="G8" s="151"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="132"/>
-      <c r="E9" s="132"/>
-      <c r="F9" s="132"/>
-      <c r="G9" s="132"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="151"/>
+      <c r="G9" s="151"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B10" s="132"/>
-      <c r="C10" s="132"/>
-      <c r="D10" s="132"/>
-      <c r="E10" s="132"/>
-      <c r="F10" s="132"/>
-      <c r="G10" s="132"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="151"/>
+      <c r="D10" s="151"/>
+      <c r="E10" s="151"/>
+      <c r="F10" s="151"/>
+      <c r="G10" s="151"/>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B11" s="132"/>
-      <c r="C11" s="132"/>
-      <c r="D11" s="132"/>
-      <c r="E11" s="132"/>
-      <c r="F11" s="132"/>
-      <c r="G11" s="132"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="151"/>
+      <c r="D11" s="151"/>
+      <c r="E11" s="151"/>
+      <c r="F11" s="151"/>
+      <c r="G11" s="151"/>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B12" s="132"/>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132"/>
-      <c r="E12" s="132"/>
-      <c r="F12" s="132"/>
-      <c r="G12" s="132"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="151"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="151"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B13" s="132"/>
-      <c r="C13" s="132"/>
-      <c r="D13" s="132"/>
-      <c r="E13" s="132"/>
-      <c r="F13" s="132"/>
-      <c r="G13" s="132"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="151"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="151"/>
+      <c r="F13" s="151"/>
+      <c r="G13" s="151"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132"/>
-      <c r="E14" s="132"/>
-      <c r="F14" s="132"/>
-      <c r="G14" s="132"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="151"/>
+      <c r="D14" s="151"/>
+      <c r="E14" s="151"/>
+      <c r="F14" s="151"/>
+      <c r="G14" s="151"/>
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B15" s="132"/>
-      <c r="C15" s="132"/>
-      <c r="D15" s="132"/>
-      <c r="E15" s="132"/>
-      <c r="F15" s="132"/>
-      <c r="G15" s="132"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="151"/>
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.2">
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132"/>
-      <c r="E16" s="132"/>
-      <c r="F16" s="132"/>
-      <c r="G16" s="132"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="151"/>
+      <c r="D16" s="151"/>
+      <c r="E16" s="151"/>
+      <c r="F16" s="151"/>
+      <c r="G16" s="151"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B17" s="132"/>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132"/>
-      <c r="E17" s="132"/>
-      <c r="F17" s="132"/>
-      <c r="G17" s="132"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="151"/>
+      <c r="D17" s="151"/>
+      <c r="E17" s="151"/>
+      <c r="F17" s="151"/>
+      <c r="G17" s="151"/>
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B18" s="132"/>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132"/>
-      <c r="E18" s="132"/>
-      <c r="F18" s="132"/>
-      <c r="G18" s="132"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="151"/>
+      <c r="D18" s="151"/>
+      <c r="E18" s="151"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="151"/>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B19" s="132"/>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132"/>
-      <c r="E19" s="132"/>
-      <c r="F19" s="132"/>
-      <c r="G19" s="132"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="151"/>
+      <c r="D19" s="151"/>
+      <c r="E19" s="151"/>
+      <c r="F19" s="151"/>
+      <c r="G19" s="151"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B20" s="132"/>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132"/>
-      <c r="E20" s="132"/>
-      <c r="F20" s="132"/>
-      <c r="G20" s="132"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="151"/>
+      <c r="D20" s="151"/>
+      <c r="E20" s="151"/>
+      <c r="F20" s="151"/>
+      <c r="G20" s="151"/>
     </row>
     <row r="21" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B21" s="132"/>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132"/>
-      <c r="E21" s="132"/>
-      <c r="F21" s="132"/>
-      <c r="G21" s="132"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="151"/>
+      <c r="D21" s="151"/>
+      <c r="E21" s="151"/>
+      <c r="F21" s="151"/>
+      <c r="G21" s="151"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B22" s="132"/>
-      <c r="C22" s="132"/>
-      <c r="D22" s="132"/>
-      <c r="E22" s="132"/>
-      <c r="F22" s="132"/>
-      <c r="G22" s="132"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="151"/>
+      <c r="D22" s="151"/>
+      <c r="E22" s="151"/>
+      <c r="F22" s="151"/>
+      <c r="G22" s="151"/>
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B23" s="132"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="132"/>
-      <c r="E23" s="132"/>
-      <c r="F23" s="132"/>
-      <c r="G23" s="132"/>
+      <c r="B23" s="151"/>
+      <c r="C23" s="151"/>
+      <c r="D23" s="151"/>
+      <c r="E23" s="151"/>
+      <c r="F23" s="151"/>
+      <c r="G23" s="151"/>
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B24" s="132"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132"/>
-      <c r="E24" s="132"/>
-      <c r="F24" s="132"/>
-      <c r="G24" s="132"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="151"/>
+      <c r="D24" s="151"/>
+      <c r="E24" s="151"/>
+      <c r="F24" s="151"/>
+      <c r="G24" s="151"/>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B25" s="132"/>
-      <c r="C25" s="132"/>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="151"/>
+      <c r="D25" s="151"/>
+      <c r="E25" s="151"/>
+      <c r="F25" s="151"/>
+      <c r="G25" s="151"/>
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B26" s="132"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="151"/>
+      <c r="D26" s="151"/>
+      <c r="E26" s="151"/>
+      <c r="F26" s="151"/>
+      <c r="G26" s="151"/>
     </row>
     <row r="27" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B27" s="132"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132"/>
-      <c r="E27" s="132"/>
-      <c r="F27" s="132"/>
-      <c r="G27" s="132"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="151"/>
+      <c r="D27" s="151"/>
+      <c r="E27" s="151"/>
+      <c r="F27" s="151"/>
+      <c r="G27" s="151"/>
     </row>
     <row r="28" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B28" s="132"/>
-      <c r="C28" s="132"/>
-      <c r="D28" s="132"/>
-      <c r="E28" s="132"/>
-      <c r="F28" s="132"/>
-      <c r="G28" s="132"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="151"/>
+      <c r="D28" s="151"/>
+      <c r="E28" s="151"/>
+      <c r="F28" s="151"/>
+      <c r="G28" s="151"/>
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B29" s="132"/>
-      <c r="C29" s="132"/>
-      <c r="D29" s="132"/>
-      <c r="E29" s="132"/>
-      <c r="F29" s="132"/>
-      <c r="G29" s="132"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="151"/>
+      <c r="D29" s="151"/>
+      <c r="E29" s="151"/>
+      <c r="F29" s="151"/>
+      <c r="G29" s="151"/>
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B30" s="132"/>
-      <c r="C30" s="132"/>
-      <c r="D30" s="132"/>
-      <c r="E30" s="132"/>
-      <c r="F30" s="132"/>
-      <c r="G30" s="132"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="151"/>
+      <c r="D30" s="151"/>
+      <c r="E30" s="151"/>
+      <c r="F30" s="151"/>
+      <c r="G30" s="151"/>
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B31" s="132"/>
-      <c r="C31" s="132"/>
-      <c r="D31" s="132"/>
-      <c r="E31" s="132"/>
-      <c r="F31" s="132"/>
-      <c r="G31" s="132"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="151"/>
+      <c r="D31" s="151"/>
+      <c r="E31" s="151"/>
+      <c r="F31" s="151"/>
+      <c r="G31" s="151"/>
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B32" s="132"/>
-      <c r="C32" s="132"/>
-      <c r="D32" s="132"/>
-      <c r="E32" s="132"/>
-      <c r="F32" s="132"/>
-      <c r="G32" s="132"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="151"/>
+      <c r="D32" s="151"/>
+      <c r="E32" s="151"/>
+      <c r="F32" s="151"/>
+      <c r="G32" s="151"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="1" selectUnlockedCells="1"/>
@@ -11099,15 +10793,15 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K1" s="100" t="s">
+      <c r="K1" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="L1" s="101"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
       <c r="P1" s="20"/>
-      <c r="Q1" s="135"/>
-      <c r="R1" s="135"/>
+      <c r="Q1" s="155"/>
+      <c r="R1" s="155"/>
     </row>
     <row r="2" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14"/>
@@ -11134,165 +10828,165 @@
       <c r="J3" s="14"/>
     </row>
     <row r="4" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="136" t="s">
+      <c r="A4" s="154" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="136"/>
-      <c r="C4" s="136"/>
-      <c r="D4" s="136"/>
-      <c r="E4" s="136"/>
-      <c r="F4" s="136"/>
-      <c r="G4" s="136"/>
-      <c r="H4" s="136"/>
-      <c r="I4" s="136"/>
-      <c r="J4" s="136"/>
+      <c r="B4" s="154"/>
+      <c r="C4" s="154"/>
+      <c r="D4" s="154"/>
+      <c r="E4" s="154"/>
+      <c r="F4" s="154"/>
+      <c r="G4" s="154"/>
+      <c r="H4" s="154"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="154"/>
     </row>
     <row r="5" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="134" t="s">
+      <c r="B5" s="153" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="134"/>
-      <c r="D5" s="134"/>
-      <c r="E5" s="134"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="134"/>
-      <c r="H5" s="134"/>
-      <c r="I5" s="134"/>
-      <c r="J5" s="134"/>
+      <c r="C5" s="153"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="153"/>
+      <c r="F5" s="153"/>
+      <c r="G5" s="153"/>
+      <c r="H5" s="153"/>
+      <c r="I5" s="153"/>
+      <c r="J5" s="153"/>
     </row>
     <row r="6" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="134" t="s">
+      <c r="B6" s="153" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="134"/>
-      <c r="D6" s="134"/>
-      <c r="E6" s="134"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="134"/>
-      <c r="H6" s="134"/>
-      <c r="I6" s="134"/>
-      <c r="J6" s="134"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="153"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="153"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="153"/>
     </row>
     <row r="7" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="134" t="s">
+      <c r="B7" s="153" t="s">
         <v>10</v>
       </c>
-      <c r="C7" s="134"/>
-      <c r="D7" s="134"/>
-      <c r="E7" s="134"/>
-      <c r="F7" s="134"/>
-      <c r="G7" s="134"/>
-      <c r="H7" s="134"/>
-      <c r="I7" s="134"/>
-      <c r="J7" s="134"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="153"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="153"/>
     </row>
     <row r="8" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="134" t="s">
+      <c r="B8" s="153" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="134"/>
-      <c r="D8" s="134"/>
-      <c r="E8" s="134"/>
-      <c r="F8" s="134"/>
-      <c r="G8" s="134"/>
-      <c r="H8" s="134"/>
-      <c r="I8" s="134"/>
-      <c r="J8" s="134"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
+      <c r="F8" s="153"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="153"/>
+      <c r="I8" s="153"/>
+      <c r="J8" s="153"/>
     </row>
     <row r="9" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B9" s="134" t="s">
+      <c r="B9" s="153" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="134"/>
-      <c r="D9" s="134"/>
-      <c r="E9" s="134"/>
-      <c r="F9" s="134"/>
-      <c r="G9" s="134"/>
-      <c r="H9" s="134"/>
-      <c r="I9" s="134"/>
-      <c r="J9" s="134"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
+      <c r="F9" s="153"/>
+      <c r="G9" s="153"/>
+      <c r="H9" s="153"/>
+      <c r="I9" s="153"/>
+      <c r="J9" s="153"/>
     </row>
     <row r="10" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="134" t="s">
+      <c r="B10" s="153" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="134"/>
-      <c r="D10" s="134"/>
-      <c r="E10" s="134"/>
-      <c r="F10" s="134"/>
-      <c r="G10" s="134"/>
-      <c r="H10" s="134"/>
-      <c r="I10" s="134"/>
-      <c r="J10" s="134"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
+      <c r="F10" s="153"/>
+      <c r="G10" s="153"/>
+      <c r="H10" s="153"/>
+      <c r="I10" s="153"/>
+      <c r="J10" s="153"/>
     </row>
     <row r="11" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B11" s="134" t="s">
+      <c r="B11" s="153" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="134"/>
-      <c r="D11" s="134"/>
-      <c r="E11" s="134"/>
-      <c r="F11" s="134"/>
-      <c r="G11" s="134"/>
-      <c r="H11" s="134"/>
-      <c r="I11" s="134"/>
-      <c r="J11" s="134"/>
-      <c r="K11" s="134"/>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
+      <c r="F11" s="153"/>
+      <c r="G11" s="153"/>
+      <c r="H11" s="153"/>
+      <c r="I11" s="153"/>
+      <c r="J11" s="153"/>
+      <c r="K11" s="153"/>
+      <c r="L11" s="153"/>
+      <c r="M11" s="153"/>
     </row>
     <row r="12" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B12" s="134" t="s">
+      <c r="B12" s="153" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="134"/>
-      <c r="D12" s="134"/>
-      <c r="E12" s="134"/>
-      <c r="F12" s="134"/>
-      <c r="G12" s="134"/>
-      <c r="H12" s="134"/>
-      <c r="I12" s="134"/>
-      <c r="J12" s="134"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
+      <c r="F12" s="153"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="153"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="153"/>
     </row>
     <row r="13" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="134" t="s">
+      <c r="B13" s="153" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="134"/>
-      <c r="D13" s="134"/>
-      <c r="E13" s="134"/>
-      <c r="F13" s="134"/>
-      <c r="G13" s="134"/>
-      <c r="H13" s="134"/>
-      <c r="I13" s="134"/>
-      <c r="J13" s="134"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
+      <c r="F13" s="153"/>
+      <c r="G13" s="153"/>
+      <c r="H13" s="153"/>
+      <c r="I13" s="153"/>
+      <c r="J13" s="153"/>
     </row>
     <row r="14" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="12"/>
@@ -11307,54 +11001,54 @@
       <c r="J14" s="13"/>
     </row>
     <row r="15" spans="1:18" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="136" t="s">
+      <c r="A15" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="136"/>
-      <c r="C15" s="136"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="136"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="136"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="136"/>
-      <c r="J15" s="136"/>
+      <c r="B15" s="154"/>
+      <c r="C15" s="154"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="154"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="154"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="154"/>
+      <c r="J15" s="154"/>
     </row>
     <row r="16" spans="1:18" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B16" s="134" t="s">
+      <c r="B16" s="153" t="s">
         <v>56</v>
       </c>
-      <c r="C16" s="134"/>
-      <c r="D16" s="134"/>
-      <c r="E16" s="134"/>
-      <c r="F16" s="134"/>
-      <c r="G16" s="134"/>
-      <c r="H16" s="134"/>
-      <c r="I16" s="134"/>
-      <c r="J16" s="134"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
+      <c r="F16" s="153"/>
+      <c r="G16" s="153"/>
+      <c r="H16" s="153"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="153"/>
     </row>
     <row r="17" spans="1:19" s="10" customFormat="1" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B17" s="134" t="s">
+      <c r="B17" s="153" t="s">
         <v>18</v>
       </c>
-      <c r="C17" s="134"/>
-      <c r="D17" s="134"/>
-      <c r="E17" s="134"/>
-      <c r="F17" s="134"/>
-      <c r="G17" s="134"/>
-      <c r="H17" s="134"/>
-      <c r="I17" s="134"/>
-      <c r="J17" s="134"/>
-      <c r="K17" s="134"/>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
-      <c r="N17" s="134"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
+      <c r="F17" s="153"/>
+      <c r="G17" s="153"/>
+      <c r="H17" s="153"/>
+      <c r="I17" s="153"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
+      <c r="M17" s="153"/>
+      <c r="N17" s="153"/>
       <c r="O17" s="28"/>
       <c r="P17" s="28"/>
     </row>
@@ -11362,21 +11056,21 @@
       <c r="A18" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="153" t="s">
         <v>19</v>
       </c>
-      <c r="C18" s="134"/>
-      <c r="D18" s="134"/>
-      <c r="E18" s="134"/>
-      <c r="F18" s="134"/>
-      <c r="G18" s="134"/>
-      <c r="H18" s="134"/>
-      <c r="I18" s="134"/>
-      <c r="J18" s="134"/>
-      <c r="K18" s="134"/>
-      <c r="L18" s="134"/>
-      <c r="M18" s="134"/>
-      <c r="N18" s="134"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
+      <c r="F18" s="153"/>
+      <c r="G18" s="153"/>
+      <c r="H18" s="153"/>
+      <c r="I18" s="153"/>
+      <c r="J18" s="153"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
+      <c r="M18" s="153"/>
+      <c r="N18" s="153"/>
       <c r="O18" s="33"/>
       <c r="P18" s="33"/>
       <c r="Q18" s="33"/>
@@ -11387,101 +11081,101 @@
       <c r="A19" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="134" t="s">
+      <c r="B19" s="153" t="s">
         <v>20</v>
       </c>
-      <c r="C19" s="134"/>
-      <c r="D19" s="134"/>
-      <c r="E19" s="134"/>
-      <c r="F19" s="134"/>
-      <c r="G19" s="134"/>
-      <c r="H19" s="134"/>
-      <c r="I19" s="134"/>
-      <c r="J19" s="134"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
+      <c r="F19" s="153"/>
+      <c r="G19" s="153"/>
+      <c r="H19" s="153"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="153"/>
     </row>
     <row r="20" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B20" s="134" t="s">
+      <c r="B20" s="153" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="134"/>
-      <c r="D20" s="134"/>
-      <c r="E20" s="134"/>
-      <c r="F20" s="134"/>
-      <c r="G20" s="134"/>
-      <c r="H20" s="134"/>
-      <c r="I20" s="134"/>
-      <c r="J20" s="134"/>
-      <c r="K20" s="134"/>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
+      <c r="F20" s="153"/>
+      <c r="G20" s="153"/>
+      <c r="H20" s="153"/>
+      <c r="I20" s="153"/>
+      <c r="J20" s="153"/>
+      <c r="K20" s="153"/>
+      <c r="L20" s="153"/>
+      <c r="M20" s="153"/>
     </row>
     <row r="21" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B21" s="134" t="s">
+      <c r="B21" s="153" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="134"/>
-      <c r="D21" s="134"/>
-      <c r="E21" s="134"/>
-      <c r="F21" s="134"/>
-      <c r="G21" s="134"/>
-      <c r="H21" s="134"/>
-      <c r="I21" s="134"/>
-      <c r="J21" s="134"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
+      <c r="F21" s="153"/>
+      <c r="G21" s="153"/>
+      <c r="H21" s="153"/>
+      <c r="I21" s="153"/>
+      <c r="J21" s="153"/>
     </row>
     <row r="22" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="134" t="s">
+      <c r="B22" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="C22" s="134"/>
-      <c r="D22" s="134"/>
-      <c r="E22" s="134"/>
-      <c r="F22" s="134"/>
-      <c r="G22" s="134"/>
-      <c r="H22" s="134"/>
-      <c r="I22" s="134"/>
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
+      <c r="F22" s="153"/>
+      <c r="G22" s="153"/>
+      <c r="H22" s="153"/>
+      <c r="I22" s="153"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
     </row>
     <row r="23" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="134" t="s">
+      <c r="B23" s="153" t="s">
         <v>92</v>
       </c>
-      <c r="C23" s="134"/>
-      <c r="D23" s="134"/>
-      <c r="E23" s="134"/>
-      <c r="F23" s="134"/>
-      <c r="G23" s="134"/>
-      <c r="H23" s="134"/>
-      <c r="I23" s="134"/>
-      <c r="J23" s="134"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="153"/>
+      <c r="H23" s="153"/>
+      <c r="I23" s="153"/>
+      <c r="J23" s="153"/>
     </row>
     <row r="24" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="134" t="s">
+      <c r="B24" s="153" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="134"/>
-      <c r="D24" s="134"/>
-      <c r="E24" s="134"/>
-      <c r="F24" s="134"/>
-      <c r="G24" s="134"/>
-      <c r="H24" s="134"/>
-      <c r="I24" s="134"/>
-      <c r="J24" s="134"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
+      <c r="F24" s="153"/>
+      <c r="G24" s="153"/>
+      <c r="H24" s="153"/>
+      <c r="I24" s="153"/>
+      <c r="J24" s="153"/>
     </row>
     <row r="25" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
@@ -11496,56 +11190,56 @@
       <c r="J25" s="13"/>
     </row>
     <row r="26" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="136" t="s">
+      <c r="A26" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="136"/>
-      <c r="C26" s="136"/>
-      <c r="D26" s="136"/>
-      <c r="E26" s="136"/>
-      <c r="F26" s="136"/>
-      <c r="G26" s="136"/>
-      <c r="H26" s="136"/>
-      <c r="I26" s="136"/>
-      <c r="J26" s="136"/>
+      <c r="B26" s="154"/>
+      <c r="C26" s="154"/>
+      <c r="D26" s="154"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="154"/>
     </row>
     <row r="27" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="134" t="s">
+      <c r="B27" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="C27" s="134"/>
-      <c r="D27" s="134"/>
-      <c r="E27" s="134"/>
-      <c r="F27" s="134"/>
-      <c r="G27" s="134"/>
-      <c r="H27" s="134"/>
-      <c r="I27" s="134"/>
-      <c r="J27" s="134"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
+      <c r="F27" s="153"/>
+      <c r="G27" s="153"/>
+      <c r="H27" s="153"/>
+      <c r="I27" s="153"/>
+      <c r="J27" s="153"/>
     </row>
     <row r="28" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="134" t="s">
+      <c r="B28" s="153" t="s">
         <v>27</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="134"/>
-      <c r="E28" s="134"/>
-      <c r="F28" s="134"/>
-      <c r="G28" s="134"/>
-      <c r="H28" s="134"/>
-      <c r="I28" s="134"/>
-      <c r="J28" s="134"/>
-      <c r="K28" s="134"/>
-      <c r="L28" s="134"/>
-      <c r="M28" s="134"/>
-      <c r="N28" s="134"/>
-      <c r="O28" s="134"/>
-      <c r="P28" s="134"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
+      <c r="F28" s="153"/>
+      <c r="G28" s="153"/>
+      <c r="H28" s="153"/>
+      <c r="I28" s="153"/>
+      <c r="J28" s="153"/>
+      <c r="K28" s="153"/>
+      <c r="L28" s="153"/>
+      <c r="M28" s="153"/>
+      <c r="N28" s="153"/>
+      <c r="O28" s="153"/>
+      <c r="P28" s="153"/>
       <c r="Q28" s="10"/>
       <c r="R28" s="10"/>
       <c r="S28" s="10"/>
@@ -11554,139 +11248,139 @@
       <c r="A29" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="134" t="s">
+      <c r="B29" s="153" t="s">
         <v>28</v>
       </c>
-      <c r="C29" s="134"/>
-      <c r="D29" s="134"/>
-      <c r="E29" s="134"/>
-      <c r="F29" s="134"/>
-      <c r="G29" s="134"/>
-      <c r="H29" s="134"/>
-      <c r="I29" s="134"/>
-      <c r="J29" s="134"/>
-      <c r="K29" s="134"/>
-      <c r="L29" s="134"/>
-      <c r="M29" s="134"/>
-      <c r="N29" s="134"/>
-      <c r="O29" s="134"/>
-      <c r="P29" s="134"/>
-      <c r="Q29" s="134"/>
-      <c r="R29" s="134"/>
-      <c r="S29" s="134"/>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
+      <c r="F29" s="153"/>
+      <c r="G29" s="153"/>
+      <c r="H29" s="153"/>
+      <c r="I29" s="153"/>
+      <c r="J29" s="153"/>
+      <c r="K29" s="153"/>
+      <c r="L29" s="153"/>
+      <c r="M29" s="153"/>
+      <c r="N29" s="153"/>
+      <c r="O29" s="153"/>
+      <c r="P29" s="153"/>
+      <c r="Q29" s="153"/>
+      <c r="R29" s="153"/>
+      <c r="S29" s="153"/>
     </row>
     <row r="30" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="153" t="s">
         <v>29</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="134"/>
-      <c r="E30" s="134"/>
-      <c r="F30" s="134"/>
-      <c r="G30" s="134"/>
-      <c r="H30" s="134"/>
-      <c r="I30" s="134"/>
-      <c r="J30" s="134"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
+      <c r="F30" s="153"/>
+      <c r="G30" s="153"/>
+      <c r="H30" s="153"/>
+      <c r="I30" s="153"/>
+      <c r="J30" s="153"/>
     </row>
     <row r="31" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="134" t="s">
+      <c r="B31" s="153" t="s">
         <v>30</v>
       </c>
-      <c r="C31" s="134"/>
-      <c r="D31" s="134"/>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="134"/>
-      <c r="J31" s="134"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
+      <c r="F31" s="153"/>
+      <c r="G31" s="153"/>
+      <c r="H31" s="153"/>
+      <c r="I31" s="153"/>
+      <c r="J31" s="153"/>
     </row>
     <row r="32" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="134" t="s">
+      <c r="B32" s="153" t="s">
         <v>31</v>
       </c>
-      <c r="C32" s="134"/>
-      <c r="D32" s="134"/>
-      <c r="E32" s="134"/>
-      <c r="F32" s="134"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="134"/>
-      <c r="J32" s="134"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
+      <c r="F32" s="153"/>
+      <c r="G32" s="153"/>
+      <c r="H32" s="153"/>
+      <c r="I32" s="153"/>
+      <c r="J32" s="153"/>
     </row>
     <row r="33" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="12"/>
-      <c r="B33" s="134"/>
-      <c r="C33" s="134"/>
-      <c r="D33" s="134"/>
-      <c r="E33" s="134"/>
-      <c r="F33" s="134"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="134"/>
-      <c r="J33" s="134"/>
-      <c r="K33" s="134"/>
+      <c r="B33" s="153"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
+      <c r="F33" s="153"/>
+      <c r="G33" s="153"/>
+      <c r="H33" s="153"/>
+      <c r="I33" s="153"/>
+      <c r="J33" s="153"/>
+      <c r="K33" s="153"/>
     </row>
     <row r="34" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="136" t="s">
+      <c r="A34" s="154" t="s">
         <v>32</v>
       </c>
-      <c r="B34" s="136"/>
-      <c r="C34" s="136"/>
-      <c r="D34" s="136"/>
-      <c r="E34" s="136"/>
-      <c r="F34" s="136"/>
-      <c r="G34" s="136"/>
-      <c r="H34" s="136"/>
-      <c r="I34" s="136"/>
-      <c r="J34" s="136"/>
+      <c r="B34" s="154"/>
+      <c r="C34" s="154"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="154"/>
+      <c r="F34" s="154"/>
+      <c r="G34" s="154"/>
+      <c r="H34" s="154"/>
+      <c r="I34" s="154"/>
+      <c r="J34" s="154"/>
     </row>
     <row r="35" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B35" s="134" t="s">
+      <c r="B35" s="153" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="134"/>
-      <c r="D35" s="134"/>
-      <c r="E35" s="134"/>
-      <c r="F35" s="134"/>
-      <c r="G35" s="134"/>
-      <c r="H35" s="134"/>
-      <c r="I35" s="134"/>
-      <c r="J35" s="134"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
+      <c r="F35" s="153"/>
+      <c r="G35" s="153"/>
+      <c r="H35" s="153"/>
+      <c r="I35" s="153"/>
+      <c r="J35" s="153"/>
     </row>
     <row r="36" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="134" t="s">
+      <c r="B36" s="153" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="134"/>
-      <c r="D36" s="134"/>
-      <c r="E36" s="134"/>
-      <c r="F36" s="134"/>
-      <c r="G36" s="134"/>
-      <c r="H36" s="134"/>
-      <c r="I36" s="134"/>
-      <c r="J36" s="134"/>
-      <c r="K36" s="134"/>
-      <c r="L36" s="134"/>
-      <c r="M36" s="134"/>
-      <c r="N36" s="134"/>
-      <c r="O36" s="134"/>
-      <c r="P36" s="134"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
+      <c r="F36" s="153"/>
+      <c r="G36" s="153"/>
+      <c r="H36" s="153"/>
+      <c r="I36" s="153"/>
+      <c r="J36" s="153"/>
+      <c r="K36" s="153"/>
+      <c r="L36" s="153"/>
+      <c r="M36" s="153"/>
+      <c r="N36" s="153"/>
+      <c r="O36" s="153"/>
+      <c r="P36" s="153"/>
       <c r="Q36" s="10"/>
       <c r="R36" s="10"/>
       <c r="S36" s="10"/>
@@ -11695,46 +11389,46 @@
       <c r="A37" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B37" s="134" t="s">
+      <c r="B37" s="153" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="134"/>
-      <c r="D37" s="134"/>
-      <c r="E37" s="134"/>
-      <c r="F37" s="134"/>
-      <c r="G37" s="134"/>
-      <c r="H37" s="134"/>
-      <c r="I37" s="134"/>
-      <c r="J37" s="134"/>
-      <c r="K37" s="134"/>
-      <c r="L37" s="134"/>
-      <c r="M37" s="134"/>
-      <c r="N37" s="134"/>
-      <c r="O37" s="134"/>
-      <c r="P37" s="134"/>
-      <c r="Q37" s="134"/>
-      <c r="R37" s="134"/>
-      <c r="S37" s="134"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="153"/>
+      <c r="E37" s="153"/>
+      <c r="F37" s="153"/>
+      <c r="G37" s="153"/>
+      <c r="H37" s="153"/>
+      <c r="I37" s="153"/>
+      <c r="J37" s="153"/>
+      <c r="K37" s="153"/>
+      <c r="L37" s="153"/>
+      <c r="M37" s="153"/>
+      <c r="N37" s="153"/>
+      <c r="O37" s="153"/>
+      <c r="P37" s="153"/>
+      <c r="Q37" s="153"/>
+      <c r="R37" s="153"/>
+      <c r="S37" s="153"/>
     </row>
     <row r="38" spans="1:19" ht="36" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="B38" s="134" t="s">
+      <c r="B38" s="153" t="s">
         <v>137</v>
       </c>
-      <c r="C38" s="134"/>
-      <c r="D38" s="134"/>
-      <c r="E38" s="134"/>
-      <c r="F38" s="134"/>
-      <c r="G38" s="134"/>
-      <c r="H38" s="134"/>
-      <c r="I38" s="134"/>
-      <c r="J38" s="134"/>
-      <c r="K38" s="134"/>
-      <c r="L38" s="134"/>
-      <c r="M38" s="134"/>
-      <c r="N38" s="134"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
+      <c r="F38" s="153"/>
+      <c r="G38" s="153"/>
+      <c r="H38" s="153"/>
+      <c r="I38" s="153"/>
+      <c r="J38" s="153"/>
+      <c r="K38" s="153"/>
+      <c r="L38" s="153"/>
+      <c r="M38" s="153"/>
+      <c r="N38" s="153"/>
       <c r="O38" s="33"/>
       <c r="P38" s="33"/>
       <c r="Q38" s="33"/>
@@ -11744,154 +11438,154 @@
       <c r="A39" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="134" t="s">
+      <c r="B39" s="153" t="s">
         <v>36</v>
       </c>
-      <c r="C39" s="134"/>
-      <c r="D39" s="134"/>
-      <c r="E39" s="134"/>
-      <c r="F39" s="134"/>
-      <c r="G39" s="134"/>
-      <c r="H39" s="134"/>
-      <c r="I39" s="134"/>
-      <c r="J39" s="134"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="153"/>
+      <c r="H39" s="153"/>
+      <c r="I39" s="153"/>
+      <c r="J39" s="153"/>
     </row>
     <row r="40" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B40" s="134" t="s">
+      <c r="B40" s="153" t="s">
         <v>58</v>
       </c>
-      <c r="C40" s="134"/>
-      <c r="D40" s="134"/>
-      <c r="E40" s="134"/>
-      <c r="F40" s="134"/>
-      <c r="G40" s="134"/>
-      <c r="H40" s="134"/>
-      <c r="I40" s="134"/>
-      <c r="J40" s="134"/>
-      <c r="K40" s="134"/>
-      <c r="L40" s="134"/>
-      <c r="M40" s="134"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
+      <c r="F40" s="153"/>
+      <c r="G40" s="153"/>
+      <c r="H40" s="153"/>
+      <c r="I40" s="153"/>
+      <c r="J40" s="153"/>
+      <c r="K40" s="153"/>
+      <c r="L40" s="153"/>
+      <c r="M40" s="153"/>
     </row>
     <row r="41" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B41" s="134" t="s">
+      <c r="B41" s="153" t="s">
         <v>37</v>
       </c>
-      <c r="C41" s="134"/>
-      <c r="D41" s="134"/>
-      <c r="E41" s="134"/>
-      <c r="F41" s="134"/>
-      <c r="G41" s="134"/>
-      <c r="H41" s="134"/>
-      <c r="I41" s="134"/>
-      <c r="J41" s="134"/>
-      <c r="K41" s="134"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="153"/>
+      <c r="E41" s="153"/>
+      <c r="F41" s="153"/>
+      <c r="G41" s="153"/>
+      <c r="H41" s="153"/>
+      <c r="I41" s="153"/>
+      <c r="J41" s="153"/>
+      <c r="K41" s="153"/>
     </row>
     <row r="42" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B42" s="134" t="s">
+      <c r="B42" s="153" t="s">
         <v>38</v>
       </c>
-      <c r="C42" s="134"/>
-      <c r="D42" s="134"/>
-      <c r="E42" s="134"/>
-      <c r="F42" s="134"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="134"/>
-      <c r="I42" s="134"/>
-      <c r="J42" s="134"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
+      <c r="F42" s="153"/>
+      <c r="G42" s="153"/>
+      <c r="H42" s="153"/>
+      <c r="I42" s="153"/>
+      <c r="J42" s="153"/>
     </row>
     <row r="43" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B43" s="134" t="s">
+      <c r="B43" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="C43" s="134"/>
-      <c r="D43" s="134"/>
-      <c r="E43" s="134"/>
-      <c r="F43" s="134"/>
-      <c r="G43" s="134"/>
-      <c r="H43" s="134"/>
-      <c r="I43" s="134"/>
-      <c r="J43" s="134"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="153"/>
+      <c r="E43" s="153"/>
+      <c r="F43" s="153"/>
+      <c r="G43" s="153"/>
+      <c r="H43" s="153"/>
+      <c r="I43" s="153"/>
+      <c r="J43" s="153"/>
     </row>
     <row r="44" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B44" s="134" t="s">
+      <c r="B44" s="153" t="s">
         <v>40</v>
       </c>
-      <c r="C44" s="134"/>
-      <c r="D44" s="134"/>
-      <c r="E44" s="134"/>
-      <c r="F44" s="134"/>
-      <c r="G44" s="134"/>
-      <c r="H44" s="134"/>
-      <c r="I44" s="134"/>
-      <c r="J44" s="134"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="153"/>
+      <c r="E44" s="153"/>
+      <c r="F44" s="153"/>
+      <c r="G44" s="153"/>
+      <c r="H44" s="153"/>
+      <c r="I44" s="153"/>
+      <c r="J44" s="153"/>
     </row>
     <row r="45" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="46" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="136" t="s">
+      <c r="A46" s="154" t="s">
         <v>41</v>
       </c>
-      <c r="B46" s="136"/>
-      <c r="C46" s="136"/>
-      <c r="D46" s="136"/>
-      <c r="E46" s="136"/>
-      <c r="F46" s="136"/>
-      <c r="G46" s="136"/>
-      <c r="H46" s="136"/>
-      <c r="I46" s="136"/>
-      <c r="J46" s="136"/>
+      <c r="B46" s="154"/>
+      <c r="C46" s="154"/>
+      <c r="D46" s="154"/>
+      <c r="E46" s="154"/>
+      <c r="F46" s="154"/>
+      <c r="G46" s="154"/>
+      <c r="H46" s="154"/>
+      <c r="I46" s="154"/>
+      <c r="J46" s="154"/>
     </row>
     <row r="47" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B47" s="134" t="s">
+      <c r="B47" s="153" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="134"/>
-      <c r="D47" s="134"/>
-      <c r="E47" s="134"/>
-      <c r="F47" s="134"/>
-      <c r="G47" s="134"/>
-      <c r="H47" s="134"/>
-      <c r="I47" s="134"/>
-      <c r="J47" s="134"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
+      <c r="F47" s="153"/>
+      <c r="G47" s="153"/>
+      <c r="H47" s="153"/>
+      <c r="I47" s="153"/>
+      <c r="J47" s="153"/>
     </row>
     <row r="48" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B48" s="134" t="s">
+      <c r="B48" s="153" t="s">
         <v>43</v>
       </c>
-      <c r="C48" s="134"/>
-      <c r="D48" s="134"/>
-      <c r="E48" s="134"/>
-      <c r="F48" s="134"/>
-      <c r="G48" s="134"/>
-      <c r="H48" s="134"/>
-      <c r="I48" s="134"/>
-      <c r="J48" s="134"/>
-      <c r="K48" s="134"/>
-      <c r="L48" s="134"/>
-      <c r="M48" s="134"/>
-      <c r="N48" s="134"/>
-      <c r="O48" s="134"/>
-      <c r="P48" s="134"/>
+      <c r="C48" s="153"/>
+      <c r="D48" s="153"/>
+      <c r="E48" s="153"/>
+      <c r="F48" s="153"/>
+      <c r="G48" s="153"/>
+      <c r="H48" s="153"/>
+      <c r="I48" s="153"/>
+      <c r="J48" s="153"/>
+      <c r="K48" s="153"/>
+      <c r="L48" s="153"/>
+      <c r="M48" s="153"/>
+      <c r="N48" s="153"/>
+      <c r="O48" s="153"/>
+      <c r="P48" s="153"/>
       <c r="Q48" s="10"/>
       <c r="R48" s="10"/>
       <c r="S48" s="10"/>
@@ -11900,219 +11594,219 @@
       <c r="A49" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B49" s="134" t="s">
+      <c r="B49" s="153" t="s">
         <v>138</v>
       </c>
-      <c r="C49" s="134"/>
-      <c r="D49" s="134"/>
-      <c r="E49" s="134"/>
-      <c r="F49" s="134"/>
-      <c r="G49" s="134"/>
-      <c r="H49" s="134"/>
-      <c r="I49" s="134"/>
-      <c r="J49" s="134"/>
-      <c r="K49" s="134"/>
-      <c r="L49" s="134"/>
-      <c r="M49" s="134"/>
-      <c r="N49" s="134"/>
-      <c r="O49" s="134"/>
-      <c r="P49" s="134"/>
-      <c r="Q49" s="134"/>
-      <c r="R49" s="134"/>
-      <c r="S49" s="134"/>
+      <c r="C49" s="153"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="153"/>
+      <c r="F49" s="153"/>
+      <c r="G49" s="153"/>
+      <c r="H49" s="153"/>
+      <c r="I49" s="153"/>
+      <c r="J49" s="153"/>
+      <c r="K49" s="153"/>
+      <c r="L49" s="153"/>
+      <c r="M49" s="153"/>
+      <c r="N49" s="153"/>
+      <c r="O49" s="153"/>
+      <c r="P49" s="153"/>
+      <c r="Q49" s="153"/>
+      <c r="R49" s="153"/>
+      <c r="S49" s="153"/>
     </row>
     <row r="50" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A50" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B50" s="134" t="s">
+      <c r="B50" s="153" t="s">
         <v>44</v>
       </c>
-      <c r="C50" s="134"/>
-      <c r="D50" s="134"/>
-      <c r="E50" s="134"/>
-      <c r="F50" s="134"/>
-      <c r="G50" s="134"/>
-      <c r="H50" s="134"/>
-      <c r="I50" s="134"/>
-      <c r="J50" s="134"/>
-      <c r="K50" s="134"/>
-      <c r="L50" s="134"/>
-      <c r="M50" s="134"/>
-      <c r="N50" s="134"/>
-      <c r="O50" s="134"/>
-      <c r="P50" s="134"/>
-      <c r="Q50" s="134"/>
-      <c r="R50" s="134"/>
+      <c r="C50" s="153"/>
+      <c r="D50" s="153"/>
+      <c r="E50" s="153"/>
+      <c r="F50" s="153"/>
+      <c r="G50" s="153"/>
+      <c r="H50" s="153"/>
+      <c r="I50" s="153"/>
+      <c r="J50" s="153"/>
+      <c r="K50" s="153"/>
+      <c r="L50" s="153"/>
+      <c r="M50" s="153"/>
+      <c r="N50" s="153"/>
+      <c r="O50" s="153"/>
+      <c r="P50" s="153"/>
+      <c r="Q50" s="153"/>
+      <c r="R50" s="153"/>
     </row>
     <row r="51" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A51" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B51" s="134" t="s">
+      <c r="B51" s="153" t="s">
         <v>45</v>
       </c>
-      <c r="C51" s="134"/>
-      <c r="D51" s="134"/>
-      <c r="E51" s="134"/>
-      <c r="F51" s="134"/>
-      <c r="G51" s="134"/>
-      <c r="H51" s="134"/>
-      <c r="I51" s="134"/>
-      <c r="J51" s="134"/>
+      <c r="C51" s="153"/>
+      <c r="D51" s="153"/>
+      <c r="E51" s="153"/>
+      <c r="F51" s="153"/>
+      <c r="G51" s="153"/>
+      <c r="H51" s="153"/>
+      <c r="I51" s="153"/>
+      <c r="J51" s="153"/>
     </row>
     <row r="52" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A52" s="12"/>
-      <c r="B52" s="134"/>
-      <c r="C52" s="134"/>
-      <c r="D52" s="134"/>
-      <c r="E52" s="134"/>
-      <c r="F52" s="134"/>
-      <c r="G52" s="134"/>
-      <c r="H52" s="134"/>
-      <c r="I52" s="134"/>
-      <c r="J52" s="134"/>
+      <c r="B52" s="153"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
+      <c r="F52" s="153"/>
+      <c r="G52" s="153"/>
+      <c r="H52" s="153"/>
+      <c r="I52" s="153"/>
+      <c r="J52" s="153"/>
     </row>
     <row r="53" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="136" t="s">
+      <c r="A53" s="154" t="s">
         <v>46</v>
       </c>
-      <c r="B53" s="136"/>
-      <c r="C53" s="136"/>
-      <c r="D53" s="136"/>
-      <c r="E53" s="136"/>
-      <c r="F53" s="136"/>
-      <c r="G53" s="136"/>
-      <c r="H53" s="136"/>
-      <c r="I53" s="136"/>
-      <c r="J53" s="136"/>
+      <c r="B53" s="154"/>
+      <c r="C53" s="154"/>
+      <c r="D53" s="154"/>
+      <c r="E53" s="154"/>
+      <c r="F53" s="154"/>
+      <c r="G53" s="154"/>
+      <c r="H53" s="154"/>
+      <c r="I53" s="154"/>
+      <c r="J53" s="154"/>
     </row>
     <row r="54" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A54" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B54" s="134" t="s">
+      <c r="B54" s="153" t="s">
         <v>57</v>
       </c>
-      <c r="C54" s="134"/>
-      <c r="D54" s="134"/>
-      <c r="E54" s="134"/>
-      <c r="F54" s="134"/>
-      <c r="G54" s="134"/>
-      <c r="H54" s="134"/>
-      <c r="I54" s="134"/>
-      <c r="J54" s="134"/>
-      <c r="K54" s="134"/>
-      <c r="L54" s="134"/>
+      <c r="C54" s="153"/>
+      <c r="D54" s="153"/>
+      <c r="E54" s="153"/>
+      <c r="F54" s="153"/>
+      <c r="G54" s="153"/>
+      <c r="H54" s="153"/>
+      <c r="I54" s="153"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="153"/>
+      <c r="L54" s="153"/>
     </row>
     <row r="55" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="56" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="136" t="s">
+      <c r="A56" s="154" t="s">
         <v>47</v>
       </c>
-      <c r="B56" s="136"/>
-      <c r="C56" s="136"/>
-      <c r="D56" s="136"/>
-      <c r="E56" s="136"/>
-      <c r="F56" s="136"/>
-      <c r="G56" s="136"/>
-      <c r="H56" s="136"/>
-      <c r="I56" s="136"/>
-      <c r="J56" s="136"/>
+      <c r="B56" s="154"/>
+      <c r="C56" s="154"/>
+      <c r="D56" s="154"/>
+      <c r="E56" s="154"/>
+      <c r="F56" s="154"/>
+      <c r="G56" s="154"/>
+      <c r="H56" s="154"/>
+      <c r="I56" s="154"/>
+      <c r="J56" s="154"/>
     </row>
     <row r="57" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A57" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B57" s="134" t="s">
+      <c r="B57" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="C57" s="134"/>
-      <c r="D57" s="134"/>
-      <c r="E57" s="134"/>
-      <c r="F57" s="134"/>
-      <c r="G57" s="134"/>
-      <c r="H57" s="134"/>
-      <c r="I57" s="134"/>
-      <c r="J57" s="134"/>
+      <c r="C57" s="153"/>
+      <c r="D57" s="153"/>
+      <c r="E57" s="153"/>
+      <c r="F57" s="153"/>
+      <c r="G57" s="153"/>
+      <c r="H57" s="153"/>
+      <c r="I57" s="153"/>
+      <c r="J57" s="153"/>
     </row>
     <row r="58" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A58" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="134" t="s">
+      <c r="B58" s="153" t="s">
         <v>49</v>
       </c>
-      <c r="C58" s="134"/>
-      <c r="D58" s="134"/>
-      <c r="E58" s="134"/>
-      <c r="F58" s="134"/>
-      <c r="G58" s="134"/>
-      <c r="H58" s="134"/>
-      <c r="I58" s="134"/>
-      <c r="J58" s="134"/>
-      <c r="K58" s="134"/>
-      <c r="L58" s="134"/>
-      <c r="M58" s="134"/>
-      <c r="N58" s="134"/>
-      <c r="O58" s="134"/>
-      <c r="P58" s="134"/>
+      <c r="C58" s="153"/>
+      <c r="D58" s="153"/>
+      <c r="E58" s="153"/>
+      <c r="F58" s="153"/>
+      <c r="G58" s="153"/>
+      <c r="H58" s="153"/>
+      <c r="I58" s="153"/>
+      <c r="J58" s="153"/>
+      <c r="K58" s="153"/>
+      <c r="L58" s="153"/>
+      <c r="M58" s="153"/>
+      <c r="N58" s="153"/>
+      <c r="O58" s="153"/>
+      <c r="P58" s="153"/>
       <c r="Q58" s="10"/>
       <c r="R58" s="10"/>
       <c r="S58" s="10"/>
     </row>
     <row r="59" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" spans="1:19" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="136" t="s">
+      <c r="A60" s="154" t="s">
         <v>50</v>
       </c>
-      <c r="B60" s="136"/>
-      <c r="C60" s="136"/>
-      <c r="D60" s="136"/>
-      <c r="E60" s="136"/>
-      <c r="F60" s="136"/>
-      <c r="G60" s="136"/>
-      <c r="H60" s="136"/>
-      <c r="I60" s="136"/>
-      <c r="J60" s="136"/>
+      <c r="B60" s="154"/>
+      <c r="C60" s="154"/>
+      <c r="D60" s="154"/>
+      <c r="E60" s="154"/>
+      <c r="F60" s="154"/>
+      <c r="G60" s="154"/>
+      <c r="H60" s="154"/>
+      <c r="I60" s="154"/>
+      <c r="J60" s="154"/>
     </row>
     <row r="61" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A61" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B61" s="134" t="s">
+      <c r="B61" s="153" t="s">
         <v>51</v>
       </c>
-      <c r="C61" s="134"/>
-      <c r="D61" s="134"/>
-      <c r="E61" s="134"/>
-      <c r="F61" s="134"/>
-      <c r="G61" s="134"/>
-      <c r="H61" s="134"/>
-      <c r="I61" s="134"/>
-      <c r="J61" s="134"/>
+      <c r="C61" s="153"/>
+      <c r="D61" s="153"/>
+      <c r="E61" s="153"/>
+      <c r="F61" s="153"/>
+      <c r="G61" s="153"/>
+      <c r="H61" s="153"/>
+      <c r="I61" s="153"/>
+      <c r="J61" s="153"/>
     </row>
     <row r="62" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B62" s="134" t="s">
+      <c r="B62" s="153" t="s">
         <v>52</v>
       </c>
-      <c r="C62" s="134"/>
-      <c r="D62" s="134"/>
-      <c r="E62" s="134"/>
-      <c r="F62" s="134"/>
-      <c r="G62" s="134"/>
-      <c r="H62" s="134"/>
-      <c r="I62" s="134"/>
-      <c r="J62" s="134"/>
-      <c r="K62" s="134"/>
-      <c r="L62" s="134"/>
-      <c r="M62" s="134"/>
-      <c r="N62" s="134"/>
-      <c r="O62" s="134"/>
-      <c r="P62" s="134"/>
+      <c r="C62" s="153"/>
+      <c r="D62" s="153"/>
+      <c r="E62" s="153"/>
+      <c r="F62" s="153"/>
+      <c r="G62" s="153"/>
+      <c r="H62" s="153"/>
+      <c r="I62" s="153"/>
+      <c r="J62" s="153"/>
+      <c r="K62" s="153"/>
+      <c r="L62" s="153"/>
+      <c r="M62" s="153"/>
+      <c r="N62" s="153"/>
+      <c r="O62" s="153"/>
+      <c r="P62" s="153"/>
       <c r="Q62" s="10"/>
       <c r="R62" s="10"/>
       <c r="S62" s="10"/>
@@ -12121,70 +11815,104 @@
       <c r="A63" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="134" t="s">
+      <c r="B63" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="C63" s="134"/>
-      <c r="D63" s="134"/>
-      <c r="E63" s="134"/>
-      <c r="F63" s="134"/>
-      <c r="G63" s="134"/>
-      <c r="H63" s="134"/>
-      <c r="I63" s="134"/>
-      <c r="J63" s="134"/>
-      <c r="K63" s="134"/>
-      <c r="L63" s="134"/>
-      <c r="M63" s="134"/>
-      <c r="N63" s="134"/>
-      <c r="O63" s="134"/>
-      <c r="P63" s="134"/>
-      <c r="Q63" s="134"/>
-      <c r="R63" s="134"/>
-      <c r="S63" s="134"/>
+      <c r="C63" s="153"/>
+      <c r="D63" s="153"/>
+      <c r="E63" s="153"/>
+      <c r="F63" s="153"/>
+      <c r="G63" s="153"/>
+      <c r="H63" s="153"/>
+      <c r="I63" s="153"/>
+      <c r="J63" s="153"/>
+      <c r="K63" s="153"/>
+      <c r="L63" s="153"/>
+      <c r="M63" s="153"/>
+      <c r="N63" s="153"/>
+      <c r="O63" s="153"/>
+      <c r="P63" s="153"/>
+      <c r="Q63" s="153"/>
+      <c r="R63" s="153"/>
+      <c r="S63" s="153"/>
     </row>
     <row r="64" spans="1:19" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A64" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B64" s="134" t="s">
+      <c r="B64" s="153" t="s">
         <v>54</v>
       </c>
-      <c r="C64" s="134"/>
-      <c r="D64" s="134"/>
-      <c r="E64" s="134"/>
-      <c r="F64" s="134"/>
-      <c r="G64" s="134"/>
-      <c r="H64" s="134"/>
-      <c r="I64" s="134"/>
-      <c r="J64" s="134"/>
-      <c r="K64" s="134"/>
-      <c r="L64" s="134"/>
-      <c r="M64" s="134"/>
-      <c r="N64" s="134"/>
-      <c r="O64" s="134"/>
-      <c r="P64" s="134"/>
-      <c r="Q64" s="134"/>
-      <c r="R64" s="134"/>
+      <c r="C64" s="153"/>
+      <c r="D64" s="153"/>
+      <c r="E64" s="153"/>
+      <c r="F64" s="153"/>
+      <c r="G64" s="153"/>
+      <c r="H64" s="153"/>
+      <c r="I64" s="153"/>
+      <c r="J64" s="153"/>
+      <c r="K64" s="153"/>
+      <c r="L64" s="153"/>
+      <c r="M64" s="153"/>
+      <c r="N64" s="153"/>
+      <c r="O64" s="153"/>
+      <c r="P64" s="153"/>
+      <c r="Q64" s="153"/>
+      <c r="R64" s="153"/>
     </row>
     <row r="65" spans="1:10" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="12"/>
-      <c r="B65" s="134"/>
-      <c r="C65" s="134"/>
-      <c r="D65" s="134"/>
-      <c r="E65" s="134"/>
-      <c r="F65" s="134"/>
-      <c r="G65" s="134"/>
-      <c r="H65" s="134"/>
-      <c r="I65" s="134"/>
-      <c r="J65" s="134"/>
+      <c r="B65" s="153"/>
+      <c r="C65" s="153"/>
+      <c r="D65" s="153"/>
+      <c r="E65" s="153"/>
+      <c r="F65" s="153"/>
+      <c r="G65" s="153"/>
+      <c r="H65" s="153"/>
+      <c r="I65" s="153"/>
+      <c r="J65" s="153"/>
     </row>
   </sheetData>
   <mergeCells count="60">
-    <mergeCell ref="B11:M11"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="B17:N17"/>
-    <mergeCell ref="B18:N18"/>
+    <mergeCell ref="B62:P62"/>
+    <mergeCell ref="B63:S63"/>
+    <mergeCell ref="B64:R64"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="B54:L54"/>
+    <mergeCell ref="A56:J56"/>
+    <mergeCell ref="B57:J57"/>
+    <mergeCell ref="B58:P58"/>
+    <mergeCell ref="A60:J60"/>
+    <mergeCell ref="B61:J61"/>
+    <mergeCell ref="B48:P48"/>
+    <mergeCell ref="B49:S49"/>
+    <mergeCell ref="B50:R50"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B39:J39"/>
+    <mergeCell ref="B40:M40"/>
+    <mergeCell ref="A53:J53"/>
+    <mergeCell ref="B41:K41"/>
+    <mergeCell ref="B42:J42"/>
+    <mergeCell ref="B43:J43"/>
+    <mergeCell ref="B44:J44"/>
+    <mergeCell ref="A46:J46"/>
+    <mergeCell ref="B47:J47"/>
+    <mergeCell ref="B33:K33"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="B35:J35"/>
+    <mergeCell ref="B36:P36"/>
+    <mergeCell ref="B37:S37"/>
+    <mergeCell ref="B29:S29"/>
+    <mergeCell ref="B30:J30"/>
+    <mergeCell ref="B31:J31"/>
+    <mergeCell ref="B32:J32"/>
+    <mergeCell ref="B22:K22"/>
+    <mergeCell ref="B23:J23"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="A26:J26"/>
+    <mergeCell ref="B27:J27"/>
     <mergeCell ref="B38:N38"/>
     <mergeCell ref="A15:J15"/>
     <mergeCell ref="A4:J4"/>
@@ -12201,45 +11929,11 @@
     <mergeCell ref="B19:J19"/>
     <mergeCell ref="B21:J21"/>
     <mergeCell ref="B20:M20"/>
-    <mergeCell ref="B29:S29"/>
-    <mergeCell ref="B30:J30"/>
-    <mergeCell ref="B31:J31"/>
-    <mergeCell ref="B32:J32"/>
-    <mergeCell ref="B22:K22"/>
-    <mergeCell ref="B23:J23"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="A26:J26"/>
-    <mergeCell ref="B27:J27"/>
-    <mergeCell ref="B33:K33"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="B35:J35"/>
-    <mergeCell ref="B36:P36"/>
-    <mergeCell ref="B37:S37"/>
-    <mergeCell ref="B39:J39"/>
-    <mergeCell ref="B40:M40"/>
-    <mergeCell ref="A53:J53"/>
-    <mergeCell ref="B41:K41"/>
-    <mergeCell ref="B42:J42"/>
-    <mergeCell ref="B43:J43"/>
-    <mergeCell ref="B44:J44"/>
-    <mergeCell ref="A46:J46"/>
-    <mergeCell ref="B47:J47"/>
-    <mergeCell ref="B62:P62"/>
-    <mergeCell ref="B63:S63"/>
-    <mergeCell ref="B64:R64"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="A56:J56"/>
-    <mergeCell ref="B57:J57"/>
-    <mergeCell ref="B58:P58"/>
-    <mergeCell ref="A60:J60"/>
-    <mergeCell ref="B61:J61"/>
-    <mergeCell ref="B48:P48"/>
-    <mergeCell ref="B49:S49"/>
-    <mergeCell ref="B50:R50"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B11:M11"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="B17:N17"/>
+    <mergeCell ref="B18:N18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -12257,34 +11951,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="11:20" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K1" s="100" t="s">
+      <c r="K1" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="L1" s="101"/>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
+      <c r="L1" s="116"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
       <c r="O1" s="1"/>
       <c r="Q1" s="15"/>
       <c r="R1" s="20"/>
-      <c r="S1" s="135"/>
-      <c r="T1" s="135"/>
+      <c r="S1" s="155"/>
+      <c r="T1" s="155"/>
     </row>
     <row r="2" spans="11:20" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="K2" s="35"/>
-      <c r="P2" s="137"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="1"/>
       <c r="R2" s="22"/>
       <c r="S2" s="22"/>
     </row>
     <row r="3" spans="11:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K3" s="99"/>
-      <c r="P3" s="137"/>
+      <c r="K3" s="114"/>
+      <c r="P3" s="156"/>
       <c r="R3" s="22"/>
       <c r="S3" s="22"/>
     </row>
     <row r="4" spans="11:20" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="K4" s="99"/>
-      <c r="P4" s="137"/>
+      <c r="K4" s="114"/>
+      <c r="P4" s="156"/>
       <c r="R4" s="22"/>
       <c r="S4" s="22"/>
     </row>
@@ -12319,12 +12013,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="3:13" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="J1" s="100" t="s">
+      <c r="J1" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="101"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
     </row>
     <row r="2" spans="3:13" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C2" s="54"/>
@@ -12836,12 +12530,12 @@
   <sheetData>
     <row r="1" spans="1:13" ht="72" customHeight="1" x14ac:dyDescent="0.2">
       <c r="I1" s="15"/>
-      <c r="J1" s="100" t="s">
+      <c r="J1" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="101"/>
-      <c r="L1" s="99"/>
-      <c r="M1" s="99"/>
+      <c r="K1" s="116"/>
+      <c r="L1" s="114"/>
+      <c r="M1" s="114"/>
     </row>
     <row r="2" spans="1:13" ht="40" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B2" s="54"/>
@@ -12875,17 +12569,17 @@
       <c r="A4" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="102" t="s">
-        <v>471</v>
-      </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
-      <c r="J4" s="102"/>
+      <c r="B4" s="117" t="s">
+        <v>470</v>
+      </c>
+      <c r="C4" s="117"/>
+      <c r="D4" s="117"/>
+      <c r="E4" s="117"/>
+      <c r="F4" s="117"/>
+      <c r="G4" s="117"/>
+      <c r="H4" s="117"/>
+      <c r="I4" s="117"/>
+      <c r="J4" s="117"/>
       <c r="K4" s="54"/>
       <c r="L4" s="54"/>
       <c r="M4" s="54"/>
@@ -12894,65 +12588,65 @@
       <c r="A5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B5" s="102" t="s">
+      <c r="B5" s="117" t="s">
         <v>1</v>
       </c>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="102"/>
-      <c r="G5" s="102"/>
-      <c r="H5" s="102"/>
-      <c r="I5" s="102"/>
-      <c r="J5" s="102"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+      <c r="J5" s="117"/>
     </row>
     <row r="6" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B6" s="102" t="s">
+      <c r="B6" s="117" t="s">
         <v>363</v>
       </c>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="102"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="102"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="102"/>
+      <c r="C6" s="117"/>
+      <c r="D6" s="117"/>
+      <c r="E6" s="117"/>
+      <c r="F6" s="117"/>
+      <c r="G6" s="117"/>
+      <c r="H6" s="117"/>
+      <c r="I6" s="117"/>
+      <c r="J6" s="117"/>
     </row>
     <row r="7" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="117" t="s">
         <v>90</v>
       </c>
-      <c r="C7" s="102"/>
-      <c r="D7" s="102"/>
-      <c r="E7" s="102"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="102"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="102"/>
-      <c r="J7" s="102"/>
+      <c r="C7" s="117"/>
+      <c r="D7" s="117"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="117"/>
+      <c r="H7" s="117"/>
+      <c r="I7" s="117"/>
+      <c r="J7" s="117"/>
     </row>
     <row r="8" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="102" t="s">
-        <v>419</v>
-      </c>
-      <c r="C8" s="102"/>
-      <c r="D8" s="102"/>
-      <c r="E8" s="102"/>
-      <c r="F8" s="102"/>
-      <c r="G8" s="102"/>
-      <c r="H8" s="102"/>
-      <c r="I8" s="102"/>
-      <c r="J8" s="102"/>
+      <c r="B8" s="117" t="s">
+        <v>418</v>
+      </c>
+      <c r="C8" s="117"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
+      <c r="G8" s="117"/>
+      <c r="H8" s="117"/>
+      <c r="I8" s="117"/>
+      <c r="J8" s="117"/>
     </row>
     <row r="9" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="6"/>
@@ -12960,13 +12654,13 @@
       <c r="C9" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="103" t="s">
+      <c r="D9" s="118" t="s">
         <v>4</v>
       </c>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="118"/>
+      <c r="H9" s="118"/>
     </row>
     <row r="10" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="6"/>
@@ -12975,12 +12669,12 @@
       <c r="D10" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="102" t="s">
+      <c r="E10" s="117" t="s">
         <v>4</v>
       </c>
-      <c r="F10" s="102"/>
-      <c r="G10" s="102"/>
-      <c r="H10" s="102"/>
+      <c r="F10" s="117"/>
+      <c r="G10" s="117"/>
+      <c r="H10" s="117"/>
     </row>
     <row r="11" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="6"/>
@@ -12989,12 +12683,12 @@
       <c r="D11" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="102" t="s">
+      <c r="E11" s="117" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="102"/>
-      <c r="G11" s="102"/>
-      <c r="H11" s="102"/>
+      <c r="F11" s="117"/>
+      <c r="G11" s="117"/>
+      <c r="H11" s="117"/>
     </row>
     <row r="12" spans="1:13" s="7" customFormat="1" ht="20" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="6"/>
@@ -13003,12 +12697,12 @@
       <c r="D12" s="9" t="s">
         <v>2</v>
       </c>
-      <c r="E12" s="102" t="s">
+      <c r="E12" s="117" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="102"/>
+      <c r="F12" s="117"/>
+      <c r="G12" s="117"/>
+      <c r="H12" s="117"/>
     </row>
     <row r="13" spans="1:13" ht="24" x14ac:dyDescent="0.2">
       <c r="J13" s="25"/>
@@ -13055,755 +12749,760 @@
   <dimension ref="A1:Q42"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.83203125" defaultRowHeight="14" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="1.83203125" style="138" customWidth="1"/>
-    <col min="2" max="2" width="1.83203125" style="139" customWidth="1"/>
-    <col min="3" max="3" width="27.83203125" style="139" customWidth="1"/>
-    <col min="4" max="4" width="11" style="140" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" style="139"/>
-    <col min="6" max="6" width="8.6640625" style="139" customWidth="1"/>
-    <col min="7" max="7" width="2.6640625" style="139" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" style="139" customWidth="1"/>
-    <col min="9" max="9" width="12.6640625" style="139" customWidth="1"/>
-    <col min="10" max="14" width="10.83203125" style="139"/>
-    <col min="15" max="16384" width="10.83203125" style="143"/>
+    <col min="1" max="1" width="1.83203125" style="98" customWidth="1"/>
+    <col min="2" max="2" width="1.83203125" style="99" customWidth="1"/>
+    <col min="3" max="3" width="27.83203125" style="99" customWidth="1"/>
+    <col min="4" max="4" width="11" style="100" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" style="99"/>
+    <col min="6" max="6" width="8.6640625" style="99" customWidth="1"/>
+    <col min="7" max="7" width="2.6640625" style="99" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" style="99" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" style="99" customWidth="1"/>
+    <col min="10" max="14" width="10.83203125" style="99"/>
+    <col min="15" max="16384" width="10.83203125" style="103"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="80" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="F1" s="100" t="s">
+      <c r="F1" s="115" t="s">
         <v>134</v>
       </c>
-      <c r="G1" s="101"/>
-      <c r="H1" s="99"/>
-      <c r="I1" s="99"/>
-      <c r="J1" s="142"/>
+      <c r="G1" s="116"/>
+      <c r="H1" s="114"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="102"/>
     </row>
     <row r="2" spans="1:17" ht="40" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="3" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="141"/>
-      <c r="B3" s="141"/>
-      <c r="C3" s="141"/>
-      <c r="D3" s="141"/>
-      <c r="E3" s="141"/>
-      <c r="F3" s="141"/>
-      <c r="G3" s="141"/>
-      <c r="H3" s="141"/>
-      <c r="I3" s="141"/>
-      <c r="J3" s="144"/>
-      <c r="K3" s="144"/>
-      <c r="L3" s="144"/>
-      <c r="M3" s="144"/>
-    </row>
-    <row r="4" spans="1:17" s="141" customFormat="1" ht="58" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="145" t="s">
+      <c r="A3" s="101"/>
+      <c r="B3" s="101"/>
+      <c r="C3" s="101"/>
+      <c r="D3" s="101"/>
+      <c r="E3" s="101"/>
+      <c r="F3" s="101"/>
+      <c r="G3" s="101"/>
+      <c r="H3" s="101"/>
+      <c r="I3" s="101"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="104"/>
+      <c r="M3" s="104"/>
+    </row>
+    <row r="4" spans="1:17" s="101" customFormat="1" ht="58" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="146" t="s">
+      <c r="B4" s="122" t="s">
+        <v>451</v>
+      </c>
+      <c r="C4" s="122"/>
+      <c r="D4" s="122"/>
+      <c r="E4" s="122"/>
+      <c r="F4" s="122"/>
+      <c r="G4" s="122"/>
+      <c r="H4" s="122"/>
+      <c r="I4" s="122"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+    </row>
+    <row r="5" spans="1:17" s="101" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="105"/>
+      <c r="B5" s="122"/>
+      <c r="C5" s="122"/>
+      <c r="D5" s="122"/>
+      <c r="E5" s="122"/>
+      <c r="F5" s="122"/>
+      <c r="G5" s="122"/>
+      <c r="H5" s="122"/>
+      <c r="I5" s="122"/>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+    </row>
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B6" s="120" t="s">
         <v>452</v>
       </c>
-      <c r="C4" s="146"/>
-      <c r="D4" s="146"/>
-      <c r="E4" s="146"/>
-      <c r="F4" s="146"/>
-      <c r="G4" s="146"/>
-      <c r="H4" s="146"/>
-      <c r="I4" s="146"/>
-      <c r="J4" s="147"/>
-      <c r="K4" s="147"/>
-      <c r="L4" s="147"/>
-      <c r="M4" s="147"/>
-      <c r="N4" s="147"/>
-    </row>
-    <row r="5" spans="1:17" s="141" customFormat="1" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="145"/>
-      <c r="B5" s="146"/>
-      <c r="C5" s="146"/>
-      <c r="D5" s="146"/>
-      <c r="E5" s="146"/>
-      <c r="F5" s="146"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="146"/>
-      <c r="I5" s="146"/>
-      <c r="J5" s="147"/>
-      <c r="K5" s="147"/>
-      <c r="L5" s="147"/>
-      <c r="M5" s="147"/>
-      <c r="N5" s="147"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B6" s="148" t="s">
+      <c r="C6" s="120"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="108"/>
+      <c r="K6" s="108"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="108"/>
+    </row>
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A7" s="98" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7" s="119" t="s">
         <v>453</v>
       </c>
-      <c r="C6" s="148"/>
-      <c r="D6" s="148"/>
-      <c r="E6" s="148"/>
-      <c r="F6" s="148"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="149"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="149"/>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A7" s="138" t="s">
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="119"/>
+      <c r="I7" s="119"/>
+      <c r="J7" s="119"/>
+      <c r="K7" s="119"/>
+      <c r="L7" s="119"/>
+      <c r="M7" s="119"/>
+      <c r="N7" s="119"/>
+      <c r="O7" s="119"/>
+      <c r="P7" s="119"/>
+      <c r="Q7" s="119"/>
+    </row>
+    <row r="8" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B8" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="B7" s="150" t="s">
+      <c r="C8" s="121" t="s">
         <v>454</v>
       </c>
-      <c r="C7" s="150"/>
-      <c r="D7" s="150"/>
-      <c r="E7" s="150"/>
-      <c r="F7" s="150"/>
-      <c r="G7" s="150"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="150"/>
-      <c r="J7" s="150"/>
-      <c r="K7" s="150"/>
-      <c r="L7" s="150"/>
-      <c r="M7" s="150"/>
-      <c r="N7" s="150"/>
-      <c r="O7" s="150"/>
-      <c r="P7" s="150"/>
-      <c r="Q7" s="150"/>
-    </row>
-    <row r="8" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B8" s="151" t="s">
+      <c r="D8" s="121"/>
+      <c r="E8" s="121"/>
+      <c r="F8" s="121"/>
+      <c r="G8" s="121"/>
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="108"/>
+      <c r="K8" s="108"/>
+      <c r="L8" s="108"/>
+      <c r="M8" s="108"/>
+      <c r="N8" s="108"/>
+    </row>
+    <row r="9" spans="1:17" ht="98" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B9" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C8" s="152" t="s">
+      <c r="C9" s="121" t="s">
         <v>455</v>
       </c>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="152"/>
-      <c r="G8" s="152"/>
-      <c r="H8" s="152"/>
-      <c r="I8" s="152"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="149"/>
-      <c r="M8" s="149"/>
-      <c r="N8" s="149"/>
-    </row>
-    <row r="9" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B9" s="151" t="s">
+      <c r="D9" s="121"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="121"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="121"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="108"/>
+      <c r="K9" s="108"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="108"/>
+    </row>
+    <row r="10" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B10" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C10" s="121" t="s">
         <v>456</v>
       </c>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
-      <c r="F9" s="152"/>
-      <c r="G9" s="152"/>
-      <c r="H9" s="152"/>
-      <c r="I9" s="152"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="149"/>
-      <c r="L9" s="149"/>
-      <c r="M9" s="149"/>
-      <c r="N9" s="149"/>
-    </row>
-    <row r="10" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B10" s="151" t="s">
+      <c r="D10" s="121"/>
+      <c r="E10" s="121"/>
+      <c r="F10" s="121"/>
+      <c r="G10" s="121"/>
+      <c r="H10" s="121"/>
+      <c r="I10" s="121"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="108"/>
+      <c r="M10" s="108"/>
+      <c r="N10" s="108"/>
+    </row>
+    <row r="11" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B11" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="148" t="s">
+      <c r="C11" s="121" t="s">
         <v>457</v>
       </c>
-      <c r="D10" s="148"/>
-      <c r="E10" s="148"/>
-      <c r="F10" s="148"/>
-      <c r="G10" s="148"/>
-      <c r="H10" s="148"/>
-      <c r="I10" s="148"/>
-      <c r="J10" s="149"/>
-      <c r="K10" s="149"/>
-      <c r="L10" s="149"/>
-      <c r="M10" s="149"/>
-      <c r="N10" s="149"/>
-    </row>
-    <row r="11" spans="1:17" ht="90" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="151" t="s">
+      <c r="D11" s="121"/>
+      <c r="E11" s="121"/>
+      <c r="F11" s="121"/>
+      <c r="G11" s="121"/>
+      <c r="H11" s="121"/>
+      <c r="I11" s="121"/>
+      <c r="J11" s="108"/>
+      <c r="K11" s="108"/>
+      <c r="L11" s="108"/>
+      <c r="M11" s="108"/>
+      <c r="N11" s="108"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="B12" s="107"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="107"/>
+      <c r="F12" s="107"/>
+      <c r="G12" s="107"/>
+      <c r="H12" s="107"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="108"/>
+      <c r="K12" s="108"/>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="108"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C11" s="152" t="s">
+      <c r="B13" s="119" t="s">
         <v>458</v>
       </c>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
-      <c r="F11" s="152"/>
-      <c r="G11" s="152"/>
-      <c r="H11" s="152"/>
-      <c r="I11" s="152"/>
-      <c r="J11" s="149"/>
-      <c r="K11" s="149"/>
-      <c r="L11" s="149"/>
-      <c r="M11" s="149"/>
-      <c r="N11" s="149"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="B12" s="153"/>
-      <c r="C12" s="153"/>
-      <c r="D12" s="153"/>
-      <c r="E12" s="153"/>
-      <c r="F12" s="153"/>
-      <c r="G12" s="153"/>
-      <c r="H12" s="153"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="149"/>
-      <c r="L12" s="149"/>
-      <c r="M12" s="149"/>
-      <c r="N12" s="149"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A13" s="138" t="s">
+      <c r="C13" s="119"/>
+      <c r="D13" s="119"/>
+      <c r="E13" s="119"/>
+      <c r="F13" s="119"/>
+      <c r="G13" s="119"/>
+      <c r="H13" s="119"/>
+      <c r="I13" s="119"/>
+      <c r="J13" s="119"/>
+      <c r="K13" s="119"/>
+      <c r="L13" s="119"/>
+      <c r="M13" s="119"/>
+      <c r="N13" s="119"/>
+      <c r="O13" s="119"/>
+      <c r="P13" s="119"/>
+      <c r="Q13" s="119"/>
+    </row>
+    <row r="14" spans="1:17" s="112" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="111"/>
+      <c r="B14" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="B13" s="150" t="s">
+      <c r="C14" s="119" t="s">
         <v>459</v>
       </c>
-      <c r="C13" s="150"/>
-      <c r="D13" s="150"/>
-      <c r="E13" s="150"/>
-      <c r="F13" s="150"/>
-      <c r="G13" s="150"/>
-      <c r="H13" s="150"/>
-      <c r="I13" s="150"/>
-      <c r="J13" s="150"/>
-      <c r="K13" s="150"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="150"/>
-      <c r="N13" s="150"/>
-      <c r="O13" s="150"/>
-      <c r="P13" s="150"/>
-      <c r="Q13" s="150"/>
-    </row>
-    <row r="14" spans="1:17" s="156" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="154"/>
-      <c r="B14" s="155" t="s">
+      <c r="D14" s="119"/>
+      <c r="E14" s="119"/>
+      <c r="F14" s="119"/>
+      <c r="G14" s="119"/>
+      <c r="H14" s="119"/>
+      <c r="I14" s="119"/>
+      <c r="J14" s="108"/>
+      <c r="K14" s="108"/>
+      <c r="L14" s="108"/>
+      <c r="M14" s="108"/>
+      <c r="N14" s="108"/>
+      <c r="O14" s="108"/>
+      <c r="P14" s="108"/>
+      <c r="Q14" s="108"/>
+    </row>
+    <row r="15" spans="1:17" s="112" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="111"/>
+      <c r="B15" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C14" s="150" t="s">
+      <c r="C15" s="119" t="s">
         <v>460</v>
       </c>
-      <c r="D14" s="150"/>
-      <c r="E14" s="150"/>
-      <c r="F14" s="150"/>
-      <c r="G14" s="150"/>
-      <c r="H14" s="150"/>
-      <c r="I14" s="150"/>
-      <c r="J14" s="149"/>
-      <c r="K14" s="149"/>
-      <c r="L14" s="149"/>
-      <c r="M14" s="149"/>
-      <c r="N14" s="149"/>
-      <c r="O14" s="149"/>
-      <c r="P14" s="149"/>
-      <c r="Q14" s="149"/>
-    </row>
-    <row r="15" spans="1:17" s="156" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="154"/>
-      <c r="B15" s="155" t="s">
+      <c r="D15" s="119"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="119"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="119"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="108"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="108"/>
+      <c r="P15" s="108"/>
+      <c r="Q15" s="108"/>
+    </row>
+    <row r="16" spans="1:17" s="112" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="111"/>
+      <c r="B16" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="150" t="s">
+      <c r="C16" s="119" t="s">
         <v>461</v>
       </c>
-      <c r="D15" s="150"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="150"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="150"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="149"/>
-      <c r="K15" s="149"/>
-      <c r="L15" s="149"/>
-      <c r="M15" s="149"/>
-      <c r="N15" s="149"/>
-      <c r="O15" s="149"/>
-      <c r="P15" s="149"/>
-      <c r="Q15" s="149"/>
-    </row>
-    <row r="16" spans="1:17" s="156" customFormat="1" ht="38" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="154"/>
-      <c r="B16" s="155" t="s">
+      <c r="D16" s="119"/>
+      <c r="E16" s="119"/>
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="108"/>
+      <c r="K16" s="108"/>
+      <c r="L16" s="108"/>
+      <c r="M16" s="108"/>
+      <c r="N16" s="108"/>
+      <c r="O16" s="108"/>
+      <c r="P16" s="108"/>
+      <c r="Q16" s="108"/>
+    </row>
+    <row r="17" spans="1:17" s="112" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="111"/>
+      <c r="B17" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="150" t="s">
+      <c r="C17" s="119" t="s">
         <v>462</v>
       </c>
-      <c r="D16" s="150"/>
-      <c r="E16" s="150"/>
-      <c r="F16" s="150"/>
-      <c r="G16" s="150"/>
-      <c r="H16" s="150"/>
-      <c r="I16" s="150"/>
-      <c r="J16" s="149"/>
-      <c r="K16" s="149"/>
-      <c r="L16" s="149"/>
-      <c r="M16" s="149"/>
-      <c r="N16" s="149"/>
-      <c r="O16" s="149"/>
-      <c r="P16" s="149"/>
-      <c r="Q16" s="149"/>
-    </row>
-    <row r="17" spans="1:17" s="156" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A17" s="154"/>
-      <c r="B17" s="155" t="s">
+      <c r="D17" s="119"/>
+      <c r="E17" s="119"/>
+      <c r="F17" s="119"/>
+      <c r="G17" s="119"/>
+      <c r="H17" s="119"/>
+      <c r="I17" s="119"/>
+      <c r="J17" s="108"/>
+      <c r="K17" s="108"/>
+      <c r="L17" s="108"/>
+      <c r="M17" s="108"/>
+      <c r="N17" s="108"/>
+      <c r="O17" s="108"/>
+      <c r="P17" s="108"/>
+      <c r="Q17" s="108"/>
+    </row>
+    <row r="18" spans="1:17" s="112" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="111"/>
+      <c r="B18" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C17" s="150" t="s">
+      <c r="C18" s="119" t="s">
         <v>463</v>
       </c>
-      <c r="D17" s="150"/>
-      <c r="E17" s="150"/>
-      <c r="F17" s="150"/>
-      <c r="G17" s="150"/>
-      <c r="H17" s="150"/>
-      <c r="I17" s="150"/>
-      <c r="J17" s="149"/>
-      <c r="K17" s="149"/>
-      <c r="L17" s="149"/>
-      <c r="M17" s="149"/>
-      <c r="N17" s="149"/>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149"/>
-      <c r="Q17" s="149"/>
-    </row>
-    <row r="18" spans="1:17" s="156" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="154"/>
-      <c r="B18" s="155" t="s">
+      <c r="D18" s="119"/>
+      <c r="E18" s="119"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="119"/>
+      <c r="H18" s="119"/>
+      <c r="I18" s="119"/>
+      <c r="J18" s="108"/>
+      <c r="K18" s="108"/>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
+      <c r="N18" s="108"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A19" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C18" s="150" t="s">
+      <c r="B19" s="119" t="s">
         <v>464</v>
       </c>
-      <c r="D18" s="150"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="150"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="150"/>
-      <c r="I18" s="150"/>
-      <c r="J18" s="149"/>
-      <c r="K18" s="149"/>
-      <c r="L18" s="149"/>
-      <c r="M18" s="149"/>
-      <c r="N18" s="149"/>
-      <c r="O18" s="149"/>
-      <c r="P18" s="149"/>
-      <c r="Q18" s="149"/>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A19" s="138" t="s">
+      <c r="C19" s="119"/>
+      <c r="D19" s="119"/>
+      <c r="E19" s="119"/>
+      <c r="F19" s="119"/>
+      <c r="G19" s="119"/>
+      <c r="H19" s="119"/>
+      <c r="I19" s="119"/>
+      <c r="J19" s="119"/>
+      <c r="K19" s="119"/>
+      <c r="L19" s="119"/>
+      <c r="M19" s="119"/>
+      <c r="N19" s="119"/>
+      <c r="O19" s="119"/>
+      <c r="P19" s="119"/>
+      <c r="Q19" s="119"/>
+    </row>
+    <row r="20" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="B19" s="150" t="s">
+      <c r="C20" s="119" t="s">
         <v>465</v>
       </c>
-      <c r="C19" s="150"/>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="150"/>
-      <c r="G19" s="150"/>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="150"/>
-      <c r="K19" s="150"/>
-      <c r="L19" s="150"/>
-      <c r="M19" s="150"/>
-      <c r="N19" s="150"/>
-      <c r="O19" s="150"/>
-      <c r="P19" s="150"/>
-      <c r="Q19" s="150"/>
-    </row>
-    <row r="20" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="155" t="s">
+      <c r="D20" s="119"/>
+      <c r="E20" s="119"/>
+      <c r="F20" s="119"/>
+      <c r="G20" s="119"/>
+      <c r="H20" s="119"/>
+      <c r="I20" s="119"/>
+      <c r="J20" s="119"/>
+      <c r="K20" s="119"/>
+      <c r="L20" s="119"/>
+      <c r="M20" s="119"/>
+      <c r="N20" s="119"/>
+      <c r="O20" s="119"/>
+      <c r="P20" s="119"/>
+      <c r="Q20" s="119"/>
+    </row>
+    <row r="21" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C20" s="150" t="s">
+      <c r="C21" s="119" t="s">
         <v>466</v>
       </c>
-      <c r="D20" s="150"/>
-      <c r="E20" s="150"/>
-      <c r="F20" s="150"/>
-      <c r="G20" s="150"/>
-      <c r="H20" s="150"/>
-      <c r="I20" s="150"/>
-      <c r="J20" s="150"/>
-      <c r="K20" s="150"/>
-      <c r="L20" s="150"/>
-      <c r="M20" s="150"/>
-      <c r="N20" s="150"/>
-      <c r="O20" s="150"/>
-      <c r="P20" s="150"/>
-      <c r="Q20" s="150"/>
-    </row>
-    <row r="21" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="155" t="s">
+      <c r="D21" s="119"/>
+      <c r="E21" s="119"/>
+      <c r="F21" s="119"/>
+      <c r="G21" s="119"/>
+      <c r="H21" s="119"/>
+      <c r="I21" s="119"/>
+      <c r="J21" s="119"/>
+      <c r="K21" s="119"/>
+      <c r="L21" s="119"/>
+      <c r="M21" s="119"/>
+      <c r="N21" s="119"/>
+      <c r="O21" s="119"/>
+      <c r="P21" s="119"/>
+      <c r="Q21" s="119"/>
+    </row>
+    <row r="22" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B22" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C21" s="150" t="s">
+      <c r="C22" s="119" t="s">
         <v>467</v>
       </c>
-      <c r="D21" s="150"/>
-      <c r="E21" s="150"/>
-      <c r="F21" s="150"/>
-      <c r="G21" s="150"/>
-      <c r="H21" s="150"/>
-      <c r="I21" s="150"/>
-      <c r="J21" s="150"/>
-      <c r="K21" s="150"/>
-      <c r="L21" s="150"/>
-      <c r="M21" s="150"/>
-      <c r="N21" s="150"/>
-      <c r="O21" s="150"/>
-      <c r="P21" s="150"/>
-      <c r="Q21" s="150"/>
-    </row>
-    <row r="22" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B22" s="155" t="s">
+      <c r="D22" s="119"/>
+      <c r="E22" s="119"/>
+      <c r="F22" s="119"/>
+      <c r="G22" s="119"/>
+      <c r="H22" s="119"/>
+      <c r="I22" s="119"/>
+      <c r="J22" s="119"/>
+      <c r="K22" s="119"/>
+      <c r="L22" s="119"/>
+      <c r="M22" s="119"/>
+      <c r="N22" s="119"/>
+      <c r="O22" s="119"/>
+      <c r="P22" s="119"/>
+      <c r="Q22" s="119"/>
+    </row>
+    <row r="23" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B23" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="150" t="s">
+      <c r="C23" s="119" t="s">
         <v>468</v>
       </c>
-      <c r="D22" s="150"/>
-      <c r="E22" s="150"/>
-      <c r="F22" s="150"/>
-      <c r="G22" s="150"/>
-      <c r="H22" s="150"/>
-      <c r="I22" s="150"/>
-      <c r="J22" s="150"/>
-      <c r="K22" s="150"/>
-      <c r="L22" s="150"/>
-      <c r="M22" s="150"/>
-      <c r="N22" s="150"/>
-      <c r="O22" s="150"/>
-      <c r="P22" s="150"/>
-      <c r="Q22" s="150"/>
-    </row>
-    <row r="23" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="155" t="s">
+      <c r="D23" s="119"/>
+      <c r="E23" s="119"/>
+      <c r="F23" s="119"/>
+      <c r="G23" s="119"/>
+      <c r="H23" s="119"/>
+      <c r="I23" s="119"/>
+      <c r="J23" s="119"/>
+      <c r="K23" s="119"/>
+      <c r="L23" s="119"/>
+      <c r="M23" s="119"/>
+      <c r="N23" s="119"/>
+      <c r="O23" s="119"/>
+      <c r="P23" s="119"/>
+      <c r="Q23" s="119"/>
+    </row>
+    <row r="24" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B24" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C23" s="150" t="s">
+      <c r="C24" s="119" t="s">
         <v>469</v>
       </c>
-      <c r="D23" s="150"/>
-      <c r="E23" s="150"/>
-      <c r="F23" s="150"/>
-      <c r="G23" s="150"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="150"/>
-      <c r="J23" s="150"/>
-      <c r="K23" s="150"/>
-      <c r="L23" s="150"/>
-      <c r="M23" s="150"/>
-      <c r="N23" s="150"/>
-      <c r="O23" s="150"/>
-      <c r="P23" s="150"/>
-      <c r="Q23" s="150"/>
-    </row>
-    <row r="24" spans="1:17" ht="20" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="155" t="s">
+      <c r="D24" s="119"/>
+      <c r="E24" s="119"/>
+      <c r="F24" s="119"/>
+      <c r="G24" s="119"/>
+      <c r="H24" s="119"/>
+      <c r="I24" s="119"/>
+      <c r="J24" s="119"/>
+      <c r="K24" s="119"/>
+      <c r="L24" s="119"/>
+      <c r="M24" s="119"/>
+      <c r="N24" s="119"/>
+      <c r="O24" s="119"/>
+      <c r="P24" s="119"/>
+      <c r="Q24" s="119"/>
+    </row>
+    <row r="25" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="109"/>
+      <c r="C25" s="109"/>
+      <c r="D25" s="109"/>
+      <c r="E25" s="109"/>
+      <c r="F25" s="109"/>
+      <c r="G25" s="111"/>
+      <c r="H25" s="111"/>
+      <c r="I25" s="111"/>
+      <c r="J25" s="111"/>
+      <c r="K25" s="103"/>
+      <c r="L25" s="109"/>
+      <c r="M25" s="109"/>
+      <c r="N25" s="109"/>
+    </row>
+    <row r="26" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="109"/>
+      <c r="C26" s="109"/>
+      <c r="D26" s="109"/>
+      <c r="E26" s="109"/>
+      <c r="F26" s="111"/>
+      <c r="G26" s="111"/>
+      <c r="H26" s="111"/>
+      <c r="I26" s="111"/>
+      <c r="J26" s="103"/>
+      <c r="K26" s="109"/>
+      <c r="L26" s="109"/>
+      <c r="M26" s="109"/>
+      <c r="N26" s="109"/>
+    </row>
+    <row r="27" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B27" s="109"/>
+      <c r="C27" s="109"/>
+      <c r="D27" s="109"/>
+      <c r="E27" s="109"/>
+      <c r="F27" s="109"/>
+      <c r="G27" s="109"/>
+      <c r="H27" s="109"/>
+      <c r="I27" s="109"/>
+      <c r="J27" s="109"/>
+      <c r="K27" s="109"/>
+      <c r="L27" s="109"/>
+      <c r="M27" s="109"/>
+      <c r="N27" s="109"/>
+    </row>
+    <row r="28" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="109"/>
+      <c r="C28" s="109"/>
+      <c r="D28" s="109"/>
+      <c r="E28" s="109"/>
+      <c r="F28" s="109"/>
+      <c r="G28" s="109"/>
+      <c r="H28" s="109"/>
+      <c r="I28" s="109"/>
+      <c r="J28" s="109"/>
+      <c r="K28" s="109"/>
+      <c r="L28" s="109"/>
+      <c r="M28" s="109"/>
+      <c r="N28" s="109"/>
+    </row>
+    <row r="29" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="109"/>
+      <c r="C29" s="109"/>
+      <c r="D29" s="109"/>
+      <c r="E29" s="109"/>
+      <c r="F29" s="109"/>
+      <c r="G29" s="109"/>
+      <c r="H29" s="109"/>
+      <c r="I29" s="109"/>
+      <c r="J29" s="109"/>
+      <c r="K29" s="109"/>
+      <c r="L29" s="109"/>
+      <c r="M29" s="109"/>
+      <c r="N29" s="109"/>
+    </row>
+    <row r="30" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B30" s="109"/>
+      <c r="C30" s="109"/>
+      <c r="D30" s="109"/>
+      <c r="E30" s="109"/>
+      <c r="F30" s="109"/>
+      <c r="G30" s="109"/>
+      <c r="H30" s="109"/>
+      <c r="I30" s="109"/>
+      <c r="J30" s="109"/>
+      <c r="K30" s="109"/>
+      <c r="L30" s="109"/>
+      <c r="M30" s="109"/>
+      <c r="N30" s="109"/>
+    </row>
+    <row r="31" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="109"/>
+      <c r="C31" s="109"/>
+      <c r="D31" s="109"/>
+      <c r="E31" s="109"/>
+      <c r="F31" s="109"/>
+      <c r="G31" s="109"/>
+      <c r="H31" s="109"/>
+      <c r="I31" s="109"/>
+      <c r="J31" s="109"/>
+      <c r="K31" s="109"/>
+      <c r="L31" s="109"/>
+      <c r="M31" s="109"/>
+      <c r="N31" s="109"/>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A32" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="150" t="s">
-        <v>470</v>
-      </c>
-      <c r="D24" s="150"/>
-      <c r="E24" s="150"/>
-      <c r="F24" s="150"/>
-      <c r="G24" s="150"/>
-      <c r="H24" s="150"/>
-      <c r="I24" s="150"/>
-      <c r="J24" s="150"/>
-      <c r="K24" s="150"/>
-      <c r="L24" s="150"/>
-      <c r="M24" s="150"/>
-      <c r="N24" s="150"/>
-      <c r="O24" s="150"/>
-      <c r="P24" s="150"/>
-      <c r="Q24" s="150"/>
-    </row>
-    <row r="25" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B25" s="155"/>
-      <c r="C25" s="155"/>
-      <c r="D25" s="155"/>
-      <c r="E25" s="155"/>
-      <c r="F25" s="155"/>
-      <c r="G25" s="154"/>
-      <c r="H25" s="154"/>
-      <c r="I25" s="154"/>
-      <c r="J25" s="154"/>
-      <c r="K25" s="143"/>
-      <c r="L25" s="155"/>
-      <c r="M25" s="155"/>
-      <c r="N25" s="155"/>
-    </row>
-    <row r="26" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="155"/>
-      <c r="C26" s="155"/>
-      <c r="D26" s="155"/>
-      <c r="E26" s="155"/>
-      <c r="F26" s="154"/>
-      <c r="G26" s="154"/>
-      <c r="H26" s="154"/>
-      <c r="I26" s="154"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="155"/>
-      <c r="L26" s="155"/>
-      <c r="M26" s="155"/>
-      <c r="N26" s="155"/>
-    </row>
-    <row r="27" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="155"/>
-      <c r="C27" s="155"/>
-      <c r="D27" s="155"/>
-      <c r="E27" s="155"/>
-      <c r="F27" s="155"/>
-      <c r="G27" s="155"/>
-      <c r="H27" s="155"/>
-      <c r="I27" s="155"/>
-      <c r="J27" s="155"/>
-      <c r="K27" s="155"/>
-      <c r="L27" s="155"/>
-      <c r="M27" s="155"/>
-      <c r="N27" s="155"/>
-    </row>
-    <row r="28" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B28" s="155"/>
-      <c r="C28" s="155"/>
-      <c r="D28" s="155"/>
-      <c r="E28" s="155"/>
-      <c r="F28" s="155"/>
-      <c r="G28" s="155"/>
-      <c r="H28" s="155"/>
-      <c r="I28" s="155"/>
-      <c r="J28" s="155"/>
-      <c r="K28" s="155"/>
-      <c r="L28" s="155"/>
-      <c r="M28" s="155"/>
-      <c r="N28" s="155"/>
-    </row>
-    <row r="29" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="155"/>
-      <c r="C29" s="155"/>
-      <c r="D29" s="155"/>
-      <c r="E29" s="155"/>
-      <c r="F29" s="155"/>
-      <c r="G29" s="155"/>
-      <c r="H29" s="155"/>
-      <c r="I29" s="155"/>
-      <c r="J29" s="155"/>
-      <c r="K29" s="155"/>
-      <c r="L29" s="155"/>
-      <c r="M29" s="155"/>
-      <c r="N29" s="155"/>
-    </row>
-    <row r="30" spans="1:17" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="155"/>
-      <c r="C30" s="155"/>
-      <c r="D30" s="155"/>
-      <c r="E30" s="155"/>
-      <c r="F30" s="155"/>
-      <c r="G30" s="155"/>
-      <c r="H30" s="155"/>
-      <c r="I30" s="155"/>
-      <c r="J30" s="155"/>
-      <c r="K30" s="155"/>
-      <c r="L30" s="155"/>
-      <c r="M30" s="155"/>
-      <c r="N30" s="155"/>
-    </row>
-    <row r="31" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B31" s="155"/>
-      <c r="C31" s="155"/>
-      <c r="D31" s="155"/>
-      <c r="E31" s="155"/>
-      <c r="F31" s="155"/>
-      <c r="G31" s="155"/>
-      <c r="H31" s="155"/>
-      <c r="I31" s="155"/>
-      <c r="J31" s="155"/>
-      <c r="K31" s="155"/>
-      <c r="L31" s="155"/>
-      <c r="M31" s="155"/>
-      <c r="N31" s="155"/>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
-      <c r="A32" s="138" t="s">
+      <c r="B32" s="109"/>
+      <c r="C32" s="109"/>
+      <c r="D32" s="109"/>
+      <c r="E32" s="109"/>
+      <c r="F32" s="109"/>
+      <c r="G32" s="109"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="109"/>
+      <c r="J32" s="109"/>
+      <c r="K32" s="109"/>
+      <c r="L32" s="109"/>
+      <c r="M32" s="109"/>
+      <c r="N32" s="109"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B33" s="109"/>
+      <c r="C33" s="109"/>
+      <c r="D33" s="109"/>
+      <c r="E33" s="109"/>
+      <c r="F33" s="109"/>
+      <c r="G33" s="109"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="109"/>
+      <c r="J33" s="109"/>
+      <c r="K33" s="109"/>
+      <c r="L33" s="109"/>
+      <c r="M33" s="109"/>
+      <c r="N33" s="109"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="B34" s="109"/>
+      <c r="C34" s="109"/>
+      <c r="D34" s="109"/>
+      <c r="E34" s="109"/>
+      <c r="F34" s="109"/>
+      <c r="G34" s="109"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="109"/>
+      <c r="J34" s="109"/>
+      <c r="K34" s="109"/>
+      <c r="L34" s="109"/>
+      <c r="M34" s="109"/>
+      <c r="N34" s="109"/>
+    </row>
+    <row r="35" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B35" s="109"/>
+      <c r="C35" s="109"/>
+      <c r="D35" s="109"/>
+      <c r="E35" s="109"/>
+      <c r="F35" s="109"/>
+      <c r="G35" s="109"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="109"/>
+      <c r="J35" s="109"/>
+      <c r="K35" s="109"/>
+      <c r="L35" s="109"/>
+      <c r="M35" s="109"/>
+      <c r="N35" s="109"/>
+    </row>
+    <row r="36" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B32" s="155"/>
-      <c r="C32" s="155"/>
-      <c r="D32" s="155"/>
-      <c r="E32" s="155"/>
-      <c r="F32" s="155"/>
-      <c r="G32" s="155"/>
-      <c r="H32" s="155"/>
-      <c r="I32" s="155"/>
-      <c r="J32" s="155"/>
-      <c r="K32" s="155"/>
-      <c r="L32" s="155"/>
-      <c r="M32" s="155"/>
-      <c r="N32" s="155"/>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B33" s="155"/>
-      <c r="C33" s="155"/>
-      <c r="D33" s="155"/>
-      <c r="E33" s="155"/>
-      <c r="F33" s="155"/>
-      <c r="G33" s="155"/>
-      <c r="H33" s="155"/>
-      <c r="I33" s="155"/>
-      <c r="J33" s="155"/>
-      <c r="K33" s="155"/>
-      <c r="L33" s="155"/>
-      <c r="M33" s="155"/>
-      <c r="N33" s="155"/>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="B34" s="155"/>
-      <c r="C34" s="155"/>
-      <c r="D34" s="155"/>
-      <c r="E34" s="155"/>
-      <c r="F34" s="155"/>
-      <c r="G34" s="155"/>
-      <c r="H34" s="155"/>
-      <c r="I34" s="155"/>
-      <c r="J34" s="155"/>
-      <c r="K34" s="155"/>
-      <c r="L34" s="155"/>
-      <c r="M34" s="155"/>
-      <c r="N34" s="155"/>
-    </row>
-    <row r="35" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B35" s="155"/>
-      <c r="C35" s="155"/>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="155"/>
-      <c r="H35" s="155"/>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="155"/>
-      <c r="M35" s="155"/>
-      <c r="N35" s="155"/>
-    </row>
-    <row r="36" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="138" t="s">
+      <c r="B36" s="109"/>
+      <c r="C36" s="109"/>
+      <c r="D36" s="109"/>
+      <c r="E36" s="109"/>
+      <c r="F36" s="109"/>
+      <c r="G36" s="109"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="109"/>
+      <c r="J36" s="109"/>
+      <c r="K36" s="109"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="109"/>
+      <c r="N36" s="109"/>
+    </row>
+    <row r="37" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B37" s="109"/>
+      <c r="C37" s="109"/>
+      <c r="D37" s="109"/>
+      <c r="E37" s="109"/>
+      <c r="F37" s="109"/>
+      <c r="G37" s="109"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="109"/>
+      <c r="J37" s="109"/>
+      <c r="K37" s="109"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="109"/>
+      <c r="N37" s="109"/>
+    </row>
+    <row r="38" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="98" t="s">
         <v>2</v>
       </c>
-      <c r="B36" s="155"/>
-      <c r="C36" s="155"/>
-      <c r="D36" s="155"/>
-      <c r="E36" s="155"/>
-      <c r="F36" s="155"/>
-      <c r="G36" s="155"/>
-      <c r="H36" s="155"/>
-      <c r="I36" s="155"/>
-      <c r="J36" s="155"/>
-      <c r="K36" s="155"/>
-      <c r="L36" s="155"/>
-      <c r="M36" s="155"/>
-      <c r="N36" s="155"/>
-    </row>
-    <row r="37" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B37" s="155"/>
-      <c r="C37" s="155"/>
-      <c r="D37" s="155"/>
-      <c r="E37" s="155"/>
-      <c r="F37" s="155"/>
-      <c r="G37" s="155"/>
-      <c r="H37" s="155"/>
-      <c r="I37" s="155"/>
-      <c r="J37" s="155"/>
-      <c r="K37" s="155"/>
-      <c r="L37" s="155"/>
-      <c r="M37" s="155"/>
-      <c r="N37" s="155"/>
-    </row>
-    <row r="38" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="138" t="s">
-        <v>2</v>
-      </c>
-      <c r="B38" s="155"/>
-      <c r="C38" s="155"/>
-      <c r="D38" s="155"/>
-      <c r="E38" s="155"/>
-      <c r="F38" s="155"/>
-      <c r="G38" s="155"/>
-      <c r="H38" s="155"/>
-      <c r="I38" s="155"/>
-      <c r="J38" s="149"/>
-      <c r="K38" s="149"/>
-      <c r="L38" s="149"/>
-      <c r="M38" s="149"/>
-      <c r="N38" s="149"/>
+      <c r="B38" s="109"/>
+      <c r="C38" s="109"/>
+      <c r="D38" s="109"/>
+      <c r="E38" s="109"/>
+      <c r="F38" s="109"/>
+      <c r="G38" s="109"/>
+      <c r="H38" s="109"/>
+      <c r="I38" s="109"/>
+      <c r="J38" s="108"/>
+      <c r="K38" s="108"/>
+      <c r="L38" s="108"/>
+      <c r="M38" s="108"/>
+      <c r="N38" s="108"/>
     </row>
     <row r="39" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C39" s="149"/>
-      <c r="D39" s="149"/>
-      <c r="E39" s="149"/>
-      <c r="F39" s="149"/>
-      <c r="G39" s="149"/>
-      <c r="H39" s="149"/>
-      <c r="I39" s="149"/>
-      <c r="J39" s="149"/>
-      <c r="K39" s="149"/>
-      <c r="L39" s="149"/>
-      <c r="M39" s="149"/>
-      <c r="N39" s="149"/>
+      <c r="C39" s="108"/>
+      <c r="D39" s="108"/>
+      <c r="E39" s="108"/>
+      <c r="F39" s="108"/>
+      <c r="G39" s="108"/>
+      <c r="H39" s="108"/>
+      <c r="I39" s="108"/>
+      <c r="J39" s="108"/>
+      <c r="K39" s="108"/>
+      <c r="L39" s="108"/>
+      <c r="M39" s="108"/>
+      <c r="N39" s="108"/>
     </row>
     <row r="40" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C40" s="149"/>
-      <c r="D40" s="149"/>
-      <c r="E40" s="149"/>
-      <c r="F40" s="149"/>
-      <c r="G40" s="149"/>
-      <c r="H40" s="149"/>
-      <c r="I40" s="149"/>
-      <c r="J40" s="149"/>
-      <c r="K40" s="149"/>
-      <c r="L40" s="149"/>
-      <c r="M40" s="149"/>
-      <c r="N40" s="149"/>
+      <c r="C40" s="108"/>
+      <c r="D40" s="108"/>
+      <c r="E40" s="108"/>
+      <c r="F40" s="108"/>
+      <c r="G40" s="108"/>
+      <c r="H40" s="108"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="108"/>
+      <c r="K40" s="108"/>
+      <c r="L40" s="108"/>
+      <c r="M40" s="108"/>
+      <c r="N40" s="108"/>
     </row>
     <row r="41" spans="1:14" ht="19" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C41" s="149"/>
-      <c r="D41" s="149"/>
-      <c r="E41" s="149"/>
-      <c r="F41" s="149"/>
-      <c r="G41" s="149"/>
-      <c r="H41" s="149"/>
-      <c r="I41" s="149"/>
-      <c r="J41" s="149"/>
-      <c r="K41" s="149"/>
-      <c r="L41" s="149"/>
-      <c r="M41" s="149"/>
-      <c r="N41" s="149"/>
+      <c r="C41" s="108"/>
+      <c r="D41" s="108"/>
+      <c r="E41" s="108"/>
+      <c r="F41" s="108"/>
+      <c r="G41" s="108"/>
+      <c r="H41" s="108"/>
+      <c r="I41" s="108"/>
+      <c r="J41" s="108"/>
+      <c r="K41" s="108"/>
+      <c r="L41" s="108"/>
+      <c r="M41" s="108"/>
+      <c r="N41" s="108"/>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="C42" s="149"/>
-      <c r="D42" s="149"/>
-      <c r="E42" s="149"/>
-      <c r="F42" s="149"/>
-      <c r="G42" s="149"/>
-      <c r="H42" s="149"/>
-      <c r="I42" s="149"/>
+      <c r="C42" s="108"/>
+      <c r="D42" s="108"/>
+      <c r="E42" s="108"/>
+      <c r="F42" s="108"/>
+      <c r="G42" s="108"/>
+      <c r="H42" s="108"/>
+      <c r="I42" s="108"/>
     </row>
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0"/>
   <mergeCells count="21">
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="B6:H6"/>
+    <mergeCell ref="B7:Q7"/>
+    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C9:I9"/>
     <mergeCell ref="C23:Q23"/>
     <mergeCell ref="C24:Q24"/>
     <mergeCell ref="F1:G1"/>
@@ -13820,11 +13519,6 @@
     <mergeCell ref="C15:I15"/>
     <mergeCell ref="C16:I16"/>
     <mergeCell ref="H1:I1"/>
-    <mergeCell ref="B4:I5"/>
-    <mergeCell ref="B6:H6"/>
-    <mergeCell ref="B7:Q7"/>
-    <mergeCell ref="C8:I8"/>
-    <mergeCell ref="C9:I9"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.17" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
@@ -13852,29 +13546,27 @@
       <c r="H1" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="99"/>
-      <c r="J1" s="99"/>
+      <c r="I1" s="114"/>
+      <c r="J1" s="114"/>
       <c r="K1" s="32"/>
-      <c r="L1" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="M1" s="99"/>
-      <c r="N1" s="99"/>
+      <c r="L1" s="42"/>
+      <c r="M1" s="114"/>
+      <c r="N1" s="114"/>
       <c r="P1"/>
       <c r="Q1"/>
       <c r="R1"/>
       <c r="T1" s="59" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="U1" s="59" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="V1" s="59"/>
       <c r="X1" s="59" t="s">
+        <v>421</v>
+      </c>
+      <c r="Y1" s="59" t="s">
         <v>422</v>
-      </c>
-      <c r="Y1" s="59" t="s">
-        <v>423</v>
       </c>
     </row>
     <row r="2" spans="1:26" ht="40" customHeight="1" x14ac:dyDescent="0.2">
@@ -13895,7 +13587,7 @@
       <c r="Q2"/>
       <c r="R2"/>
       <c r="T2" s="59" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="U2" s="59">
         <f t="shared" ref="U2:U21" si="0">COUNTIF($B$33:$B$232,$T2)</f>
@@ -13906,7 +13598,7 @@
         <v>0.1875</v>
       </c>
       <c r="X2" s="59" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="Y2" s="59">
         <f>COUNTIF($C$33:$C$232,$X2)</f>
@@ -13930,7 +13622,7 @@
       <c r="Q3"/>
       <c r="R3"/>
       <c r="T3" s="59" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U3" s="59">
         <f t="shared" si="0"/>
@@ -13941,7 +13633,7 @@
         <v>0.1328125</v>
       </c>
       <c r="X3" s="59" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Y3" s="59">
         <f>COUNTIF($C$33:$C$232,$X3)</f>
@@ -13965,7 +13657,7 @@
       <c r="Q4"/>
       <c r="R4"/>
       <c r="T4" s="59" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="U4" s="59">
         <f t="shared" si="0"/>
@@ -13976,7 +13668,7 @@
         <v>7.8125E-2</v>
       </c>
       <c r="X4" s="59" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="Y4" s="59">
         <f>COUNTIF($C$33:$C$232,$X4)</f>
@@ -14000,7 +13692,7 @@
       <c r="Q5"/>
       <c r="R5"/>
       <c r="T5" s="59" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="U5" s="59">
         <f t="shared" si="0"/>
@@ -14024,7 +13716,7 @@
       <c r="Q6"/>
       <c r="R6"/>
       <c r="T6" s="59" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="U6" s="59">
         <f t="shared" si="0"/>
@@ -14048,7 +13740,7 @@
       <c r="Q7"/>
       <c r="R7"/>
       <c r="T7" s="59" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="U7" s="59">
         <f t="shared" si="0"/>
@@ -14072,7 +13764,7 @@
       <c r="Q8"/>
       <c r="R8"/>
       <c r="T8" s="59" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="U8" s="59">
         <f t="shared" si="0"/>
@@ -14096,7 +13788,7 @@
       <c r="Q9"/>
       <c r="R9"/>
       <c r="T9" s="59" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="U9" s="59">
         <f t="shared" si="0"/>
@@ -14120,7 +13812,7 @@
       <c r="Q10"/>
       <c r="R10"/>
       <c r="T10" s="59" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="U10" s="59">
         <f t="shared" si="0"/>
@@ -14144,7 +13836,7 @@
       <c r="Q11"/>
       <c r="R11"/>
       <c r="T11" s="59" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="U11" s="59">
         <f t="shared" si="0"/>
@@ -14168,7 +13860,7 @@
       <c r="Q12"/>
       <c r="R12"/>
       <c r="T12" s="59" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="U12" s="59">
         <f t="shared" si="0"/>
@@ -14192,7 +13884,7 @@
       <c r="Q13"/>
       <c r="R13"/>
       <c r="T13" s="59" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U13" s="59">
         <f t="shared" si="0"/>
@@ -14216,7 +13908,7 @@
       <c r="Q14"/>
       <c r="R14"/>
       <c r="T14" s="59" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="U14" s="59">
         <f t="shared" si="0"/>
@@ -14240,7 +13932,7 @@
       <c r="Q15"/>
       <c r="R15"/>
       <c r="T15" s="59" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="U15" s="59">
         <f t="shared" si="0"/>
@@ -14264,7 +13956,7 @@
       <c r="Q16"/>
       <c r="R16"/>
       <c r="T16" s="59" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="U16" s="59">
         <f t="shared" si="0"/>
@@ -14288,7 +13980,7 @@
       <c r="Q17"/>
       <c r="R17"/>
       <c r="T17" s="59" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U17" s="59">
         <f t="shared" si="0"/>
@@ -14312,7 +14004,7 @@
       <c r="Q18"/>
       <c r="R18"/>
       <c r="T18" s="59" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U18" s="59">
         <f t="shared" si="0"/>
@@ -14336,7 +14028,7 @@
       <c r="Q19"/>
       <c r="R19"/>
       <c r="T19" s="59" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="U19" s="59">
         <f t="shared" si="0"/>
@@ -14360,7 +14052,7 @@
       <c r="Q20"/>
       <c r="R20"/>
       <c r="T20" s="59" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U20" s="59">
         <f t="shared" si="0"/>
@@ -14384,7 +14076,7 @@
       <c r="Q21"/>
       <c r="R21"/>
       <c r="T21" s="59" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="U21" s="59">
         <f t="shared" si="0"/>
@@ -14478,9 +14170,9 @@
       <c r="B28" s="27"/>
       <c r="C28" s="27"/>
       <c r="D28" s="27"/>
-      <c r="E28" s="104"/>
-      <c r="F28" s="104"/>
-      <c r="G28" s="104"/>
+      <c r="E28" s="123"/>
+      <c r="F28" s="123"/>
+      <c r="G28" s="123"/>
       <c r="H28" s="14"/>
       <c r="P28"/>
       <c r="Q28"/>
@@ -14500,9 +14192,9 @@
       <c r="R29"/>
     </row>
     <row r="30" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="104"/>
-      <c r="B30" s="104"/>
-      <c r="C30" s="104"/>
+      <c r="A30" s="123"/>
+      <c r="B30" s="123"/>
+      <c r="C30" s="123"/>
       <c r="D30" s="30"/>
       <c r="E30" s="24"/>
       <c r="F30" s="24"/>
@@ -14527,13 +14219,13 @@
     </row>
     <row r="32" spans="1:22" ht="17" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A32" s="57" t="s">
+        <v>419</v>
+      </c>
+      <c r="B32" s="58" t="s">
         <v>420</v>
       </c>
-      <c r="B32" s="58" t="s">
+      <c r="C32" s="58" t="s">
         <v>421</v>
-      </c>
-      <c r="C32" s="58" t="s">
-        <v>422</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19"/>
@@ -16145,16 +15837,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="72" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="O1" s="114" t="s">
+      <c r="O1" s="139" t="s">
         <v>134</v>
       </c>
-      <c r="P1" s="114"/>
+      <c r="P1" s="139"/>
       <c r="Q1" s="31"/>
       <c r="R1" s="31"/>
-      <c r="U1" s="100"/>
-      <c r="V1" s="101"/>
-      <c r="W1" s="99"/>
-      <c r="X1" s="99"/>
+      <c r="U1" s="115"/>
+      <c r="V1" s="116"/>
+      <c r="W1" s="114"/>
+      <c r="X1" s="114"/>
       <c r="Z1" s="21"/>
     </row>
     <row r="2" spans="1:26" ht="40" customHeight="1" x14ac:dyDescent="0.2">
@@ -16208,26 +15900,26 @@
       <c r="Z3" s="14"/>
     </row>
     <row r="4" spans="1:26" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="114" t="s">
+      <c r="A4" s="139" t="s">
         <v>93</v>
       </c>
-      <c r="B4" s="114"/>
-      <c r="C4" s="114"/>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114"/>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114"/>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114"/>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
-      <c r="N4" s="114"/>
-      <c r="O4" s="114"/>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
+      <c r="B4" s="139"/>
+      <c r="C4" s="139"/>
+      <c r="D4" s="139"/>
+      <c r="E4" s="139"/>
+      <c r="F4" s="139"/>
+      <c r="G4" s="139"/>
+      <c r="H4" s="139"/>
+      <c r="I4" s="139"/>
+      <c r="J4" s="139"/>
+      <c r="K4" s="139"/>
+      <c r="L4" s="139"/>
+      <c r="M4" s="139"/>
+      <c r="N4" s="139"/>
+      <c r="O4" s="139"/>
+      <c r="P4" s="139"/>
+      <c r="Q4" s="139"/>
+      <c r="R4" s="139"/>
       <c r="S4" s="32"/>
       <c r="T4" s="32"/>
       <c r="U4" s="32"/>
@@ -16238,24 +15930,24 @@
       <c r="Z4" s="14"/>
     </row>
     <row r="5" spans="1:26" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="114"/>
-      <c r="B5" s="114"/>
-      <c r="C5" s="114"/>
-      <c r="D5" s="114"/>
-      <c r="E5" s="114"/>
-      <c r="F5" s="114"/>
-      <c r="G5" s="114"/>
-      <c r="H5" s="114"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="114"/>
-      <c r="K5" s="114"/>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
-      <c r="N5" s="114"/>
-      <c r="O5" s="114"/>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
+      <c r="A5" s="139"/>
+      <c r="B5" s="139"/>
+      <c r="C5" s="139"/>
+      <c r="D5" s="139"/>
+      <c r="E5" s="139"/>
+      <c r="F5" s="139"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="139"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="139"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="139"/>
+      <c r="R5" s="139"/>
       <c r="S5" s="32"/>
       <c r="T5" s="32"/>
       <c r="U5" s="32"/>
@@ -16296,28 +15988,28 @@
     <row r="7" spans="1:26" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="44"/>
       <c r="B7" s="44"/>
-      <c r="C7" s="123" t="s">
+      <c r="C7" s="133" t="s">
         <v>364</v>
       </c>
-      <c r="D7" s="123"/>
-      <c r="E7" s="123"/>
-      <c r="F7" s="123"/>
-      <c r="G7" s="123"/>
-      <c r="H7" s="123"/>
-      <c r="I7" s="123"/>
-      <c r="J7" s="124"/>
-      <c r="K7" s="125" t="s">
+      <c r="D7" s="133"/>
+      <c r="E7" s="133"/>
+      <c r="F7" s="133"/>
+      <c r="G7" s="133"/>
+      <c r="H7" s="133"/>
+      <c r="I7" s="133"/>
+      <c r="J7" s="134"/>
+      <c r="K7" s="135" t="s">
         <v>365</v>
       </c>
-      <c r="L7" s="123"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="123"/>
-      <c r="O7" s="125" t="s">
+      <c r="L7" s="133"/>
+      <c r="M7" s="133"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="135" t="s">
         <v>366</v>
       </c>
-      <c r="P7" s="123"/>
-      <c r="Q7" s="123"/>
-      <c r="R7" s="123"/>
+      <c r="P7" s="133"/>
+      <c r="Q7" s="133"/>
+      <c r="R7" s="133"/>
       <c r="S7" s="32"/>
       <c r="T7" s="32"/>
       <c r="U7" s="32"/>
@@ -16328,177 +16020,177 @@
       <c r="Z7" s="14"/>
     </row>
     <row r="8" spans="1:26" ht="70" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107" t="s">
+      <c r="A8" s="142" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="107"/>
-      <c r="C8" s="126" t="s">
+      <c r="B8" s="142"/>
+      <c r="C8" s="136" t="s">
         <v>282</v>
       </c>
-      <c r="D8" s="126"/>
-      <c r="E8" s="126" t="s">
+      <c r="D8" s="136"/>
+      <c r="E8" s="136" t="s">
         <v>283</v>
       </c>
-      <c r="F8" s="126"/>
-      <c r="G8" s="126" t="s">
+      <c r="F8" s="136"/>
+      <c r="G8" s="136" t="s">
         <v>284</v>
       </c>
-      <c r="H8" s="126"/>
-      <c r="I8" s="126" t="s">
+      <c r="H8" s="136"/>
+      <c r="I8" s="136" t="s">
         <v>285</v>
       </c>
-      <c r="J8" s="126"/>
-      <c r="K8" s="126" t="s">
+      <c r="J8" s="136"/>
+      <c r="K8" s="136" t="s">
         <v>286</v>
       </c>
-      <c r="L8" s="126"/>
-      <c r="M8" s="126" t="s">
+      <c r="L8" s="136"/>
+      <c r="M8" s="136" t="s">
         <v>287</v>
       </c>
-      <c r="N8" s="126"/>
-      <c r="O8" s="126" t="s">
+      <c r="N8" s="136"/>
+      <c r="O8" s="136" t="s">
         <v>288</v>
       </c>
-      <c r="P8" s="126"/>
-      <c r="Q8" s="126" t="s">
+      <c r="P8" s="136"/>
+      <c r="Q8" s="136" t="s">
         <v>289</v>
       </c>
-      <c r="R8" s="126"/>
+      <c r="R8" s="136"/>
     </row>
     <row r="9" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="110"/>
-      <c r="B9" s="111"/>
-      <c r="C9" s="117"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="122"/>
-      <c r="G9" s="117"/>
-      <c r="H9" s="118"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="122"/>
-      <c r="K9" s="117"/>
-      <c r="L9" s="118"/>
-      <c r="M9" s="121"/>
-      <c r="N9" s="122"/>
-      <c r="O9" s="117"/>
-      <c r="P9" s="118"/>
-      <c r="Q9" s="121"/>
-      <c r="R9" s="122"/>
+      <c r="A9" s="145"/>
+      <c r="B9" s="146"/>
+      <c r="C9" s="131"/>
+      <c r="D9" s="132"/>
+      <c r="E9" s="137"/>
+      <c r="F9" s="138"/>
+      <c r="G9" s="131"/>
+      <c r="H9" s="132"/>
+      <c r="I9" s="137"/>
+      <c r="J9" s="138"/>
+      <c r="K9" s="131"/>
+      <c r="L9" s="132"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="138"/>
+      <c r="O9" s="131"/>
+      <c r="P9" s="132"/>
+      <c r="Q9" s="137"/>
+      <c r="R9" s="138"/>
     </row>
     <row r="10" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="108"/>
-      <c r="B10" s="109"/>
-      <c r="C10" s="115"/>
-      <c r="D10" s="116"/>
-      <c r="E10" s="119"/>
-      <c r="F10" s="120"/>
-      <c r="G10" s="115"/>
-      <c r="H10" s="116"/>
-      <c r="I10" s="119"/>
-      <c r="J10" s="120"/>
-      <c r="K10" s="115"/>
-      <c r="L10" s="116"/>
-      <c r="M10" s="119"/>
-      <c r="N10" s="120"/>
-      <c r="O10" s="115"/>
-      <c r="P10" s="116"/>
-      <c r="Q10" s="119"/>
-      <c r="R10" s="120"/>
+      <c r="A10" s="143"/>
+      <c r="B10" s="144"/>
+      <c r="C10" s="129"/>
+      <c r="D10" s="130"/>
+      <c r="E10" s="126"/>
+      <c r="F10" s="127"/>
+      <c r="G10" s="129"/>
+      <c r="H10" s="130"/>
+      <c r="I10" s="126"/>
+      <c r="J10" s="127"/>
+      <c r="K10" s="129"/>
+      <c r="L10" s="130"/>
+      <c r="M10" s="126"/>
+      <c r="N10" s="127"/>
+      <c r="O10" s="129"/>
+      <c r="P10" s="130"/>
+      <c r="Q10" s="126"/>
+      <c r="R10" s="127"/>
     </row>
     <row r="11" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="108"/>
-      <c r="B11" s="109"/>
-      <c r="C11" s="115"/>
-      <c r="D11" s="116"/>
-      <c r="E11" s="119"/>
-      <c r="F11" s="120"/>
-      <c r="G11" s="115"/>
-      <c r="H11" s="116"/>
-      <c r="I11" s="119"/>
-      <c r="J11" s="120"/>
-      <c r="K11" s="115"/>
-      <c r="L11" s="116"/>
-      <c r="M11" s="119"/>
-      <c r="N11" s="120"/>
-      <c r="O11" s="115"/>
-      <c r="P11" s="116"/>
-      <c r="Q11" s="119"/>
-      <c r="R11" s="120"/>
+      <c r="A11" s="143"/>
+      <c r="B11" s="144"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="130"/>
+      <c r="E11" s="126"/>
+      <c r="F11" s="127"/>
+      <c r="G11" s="129"/>
+      <c r="H11" s="130"/>
+      <c r="I11" s="126"/>
+      <c r="J11" s="127"/>
+      <c r="K11" s="129"/>
+      <c r="L11" s="130"/>
+      <c r="M11" s="126"/>
+      <c r="N11" s="127"/>
+      <c r="O11" s="129"/>
+      <c r="P11" s="130"/>
+      <c r="Q11" s="126"/>
+      <c r="R11" s="127"/>
     </row>
     <row r="12" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="108"/>
-      <c r="B12" s="109"/>
-      <c r="C12" s="115"/>
-      <c r="D12" s="116"/>
-      <c r="E12" s="119"/>
-      <c r="F12" s="120"/>
-      <c r="G12" s="115"/>
-      <c r="H12" s="116"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="120"/>
-      <c r="K12" s="115"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="119"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="115"/>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="119"/>
-      <c r="R12" s="120"/>
+      <c r="A12" s="143"/>
+      <c r="B12" s="144"/>
+      <c r="C12" s="129"/>
+      <c r="D12" s="130"/>
+      <c r="E12" s="126"/>
+      <c r="F12" s="127"/>
+      <c r="G12" s="129"/>
+      <c r="H12" s="130"/>
+      <c r="I12" s="126"/>
+      <c r="J12" s="127"/>
+      <c r="K12" s="129"/>
+      <c r="L12" s="130"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="127"/>
+      <c r="O12" s="129"/>
+      <c r="P12" s="130"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="127"/>
     </row>
     <row r="13" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="108"/>
-      <c r="B13" s="109"/>
-      <c r="C13" s="115"/>
-      <c r="D13" s="116"/>
-      <c r="E13" s="119"/>
-      <c r="F13" s="120"/>
-      <c r="G13" s="115"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="120"/>
-      <c r="K13" s="115"/>
-      <c r="L13" s="116"/>
-      <c r="M13" s="119"/>
-      <c r="N13" s="120"/>
-      <c r="O13" s="115"/>
-      <c r="P13" s="116"/>
-      <c r="Q13" s="119"/>
-      <c r="R13" s="120"/>
+      <c r="A13" s="143"/>
+      <c r="B13" s="144"/>
+      <c r="C13" s="129"/>
+      <c r="D13" s="130"/>
+      <c r="E13" s="126"/>
+      <c r="F13" s="127"/>
+      <c r="G13" s="129"/>
+      <c r="H13" s="130"/>
+      <c r="I13" s="126"/>
+      <c r="J13" s="127"/>
+      <c r="K13" s="129"/>
+      <c r="L13" s="130"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="127"/>
+      <c r="O13" s="129"/>
+      <c r="P13" s="130"/>
+      <c r="Q13" s="126"/>
+      <c r="R13" s="127"/>
     </row>
     <row r="14" spans="1:26" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="108"/>
-      <c r="B14" s="109"/>
-      <c r="C14" s="115"/>
-      <c r="D14" s="116"/>
-      <c r="E14" s="119"/>
-      <c r="F14" s="120"/>
-      <c r="G14" s="115"/>
-      <c r="H14" s="116"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="120"/>
-      <c r="K14" s="115"/>
-      <c r="L14" s="116"/>
-      <c r="M14" s="119"/>
-      <c r="N14" s="120"/>
-      <c r="O14" s="115"/>
-      <c r="P14" s="116"/>
-      <c r="Q14" s="119"/>
-      <c r="R14" s="120"/>
+      <c r="A14" s="143"/>
+      <c r="B14" s="144"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="130"/>
+      <c r="E14" s="126"/>
+      <c r="F14" s="127"/>
+      <c r="G14" s="129"/>
+      <c r="H14" s="130"/>
+      <c r="I14" s="126"/>
+      <c r="J14" s="127"/>
+      <c r="K14" s="129"/>
+      <c r="L14" s="130"/>
+      <c r="M14" s="126"/>
+      <c r="N14" s="127"/>
+      <c r="O14" s="129"/>
+      <c r="P14" s="130"/>
+      <c r="Q14" s="126"/>
+      <c r="R14" s="127"/>
     </row>
     <row r="17" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="112" t="s">
-        <v>447</v>
-      </c>
-      <c r="B17" s="112"/>
-      <c r="C17" s="112"/>
-      <c r="D17" s="112"/>
-      <c r="E17" s="112"/>
-      <c r="F17" s="112"/>
-      <c r="G17" s="112"/>
-      <c r="H17" s="112"/>
-      <c r="I17" s="112"/>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
+      <c r="A17" s="147" t="s">
+        <v>446</v>
+      </c>
+      <c r="B17" s="147"/>
+      <c r="C17" s="147"/>
+      <c r="D17" s="147"/>
+      <c r="E17" s="147"/>
+      <c r="F17" s="147"/>
+      <c r="G17" s="147"/>
+      <c r="H17" s="147"/>
+      <c r="I17" s="147"/>
+      <c r="J17" s="147"/>
+      <c r="K17" s="147"/>
       <c r="L17" s="63"/>
       <c r="M17" s="65"/>
       <c r="N17" s="65"/>
@@ -16508,99 +16200,99 @@
       <c r="R17" s="65"/>
     </row>
     <row r="18" spans="1:18" s="18" customFormat="1" ht="70" customHeight="1" thickTop="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="127" t="s">
+      <c r="A18" s="124" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="127"/>
-      <c r="C18" s="113" t="s">
+      <c r="B18" s="124"/>
+      <c r="C18" s="128" t="s">
         <v>282</v>
       </c>
-      <c r="D18" s="113"/>
-      <c r="E18" s="113" t="s">
+      <c r="D18" s="128"/>
+      <c r="E18" s="128" t="s">
         <v>283</v>
       </c>
-      <c r="F18" s="113"/>
-      <c r="G18" s="113" t="s">
+      <c r="F18" s="128"/>
+      <c r="G18" s="128" t="s">
         <v>284</v>
       </c>
-      <c r="H18" s="113"/>
-      <c r="I18" s="113" t="s">
+      <c r="H18" s="128"/>
+      <c r="I18" s="128" t="s">
         <v>285</v>
       </c>
-      <c r="J18" s="113"/>
-      <c r="K18" s="113" t="s">
+      <c r="J18" s="128"/>
+      <c r="K18" s="128" t="s">
         <v>286</v>
       </c>
-      <c r="L18" s="113"/>
-      <c r="M18" s="113" t="s">
+      <c r="L18" s="128"/>
+      <c r="M18" s="128" t="s">
         <v>287</v>
       </c>
-      <c r="N18" s="113"/>
-      <c r="O18" s="113" t="s">
+      <c r="N18" s="128"/>
+      <c r="O18" s="128" t="s">
         <v>288</v>
       </c>
-      <c r="P18" s="113"/>
-      <c r="Q18" s="113" t="s">
+      <c r="P18" s="128"/>
+      <c r="Q18" s="128" t="s">
         <v>289</v>
       </c>
-      <c r="R18" s="113"/>
+      <c r="R18" s="128"/>
     </row>
     <row r="19" spans="1:18" s="18" customFormat="1" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="128"/>
-      <c r="B19" s="128"/>
+      <c r="A19" s="125"/>
+      <c r="B19" s="125"/>
       <c r="C19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D19" s="94" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="E19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="F19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="G19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="J19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="L19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="M19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="N19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="O19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="P19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="Q19" s="82" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R19" s="82" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="20" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="105"/>
+      <c r="A20" s="140"/>
       <c r="B20" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C20" s="40"/>
       <c r="D20" s="83"/>
@@ -16620,9 +16312,9 @@
       <c r="R20" s="40"/>
     </row>
     <row r="21" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="106"/>
+      <c r="A21" s="141"/>
       <c r="B21" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C21" s="39"/>
       <c r="D21" s="84"/>
@@ -16642,9 +16334,9 @@
       <c r="R21" s="39"/>
     </row>
     <row r="22" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="105"/>
+      <c r="A22" s="140"/>
       <c r="B22" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C22" s="88"/>
       <c r="D22" s="89"/>
@@ -16664,9 +16356,9 @@
       <c r="R22" s="88"/>
     </row>
     <row r="23" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="106"/>
+      <c r="A23" s="141"/>
       <c r="B23" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C23" s="91"/>
       <c r="D23" s="92"/>
@@ -16686,9 +16378,9 @@
       <c r="R23" s="91"/>
     </row>
     <row r="24" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="105"/>
+      <c r="A24" s="140"/>
       <c r="B24" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C24" s="40"/>
       <c r="D24" s="83"/>
@@ -16708,9 +16400,9 @@
       <c r="R24" s="40"/>
     </row>
     <row r="25" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="106"/>
+      <c r="A25" s="141"/>
       <c r="B25" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C25" s="39"/>
       <c r="D25" s="84"/>
@@ -16730,9 +16422,9 @@
       <c r="R25" s="39"/>
     </row>
     <row r="26" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="105"/>
+      <c r="A26" s="140"/>
       <c r="B26" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C26" s="88"/>
       <c r="D26" s="89"/>
@@ -16752,9 +16444,9 @@
       <c r="R26" s="88"/>
     </row>
     <row r="27" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="106"/>
+      <c r="A27" s="141"/>
       <c r="B27" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C27" s="91"/>
       <c r="D27" s="92"/>
@@ -16774,9 +16466,9 @@
       <c r="R27" s="91"/>
     </row>
     <row r="28" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="105"/>
+      <c r="A28" s="140"/>
       <c r="B28" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C28" s="40"/>
       <c r="D28" s="83"/>
@@ -16796,9 +16488,9 @@
       <c r="R28" s="40"/>
     </row>
     <row r="29" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="106"/>
+      <c r="A29" s="141"/>
       <c r="B29" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C29" s="39"/>
       <c r="D29" s="84"/>
@@ -16818,9 +16510,9 @@
       <c r="R29" s="39"/>
     </row>
     <row r="30" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="105"/>
+      <c r="A30" s="140"/>
       <c r="B30" s="86" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="C30" s="88"/>
       <c r="D30" s="89"/>
@@ -16840,9 +16532,9 @@
       <c r="R30" s="88"/>
     </row>
     <row r="31" spans="1:18" s="18" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="106"/>
+      <c r="A31" s="141"/>
       <c r="B31" s="64" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="C31" s="91"/>
       <c r="D31" s="92"/>
@@ -16864,20 +16556,62 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0"/>
   <mergeCells count="86">
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="Q13:R13"/>
-    <mergeCell ref="Q12:R12"/>
-    <mergeCell ref="Q11:R11"/>
-    <mergeCell ref="Q18:R18"/>
-    <mergeCell ref="O14:P14"/>
-    <mergeCell ref="O13:P13"/>
-    <mergeCell ref="O12:P12"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="K18:L18"/>
-    <mergeCell ref="M18:N18"/>
-    <mergeCell ref="O18:P18"/>
+    <mergeCell ref="A30:A31"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A22:A23"/>
+    <mergeCell ref="A24:A25"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A17:K17"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="A4:R5"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="A28:A29"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="C13:D13"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="I13:J13"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="I10:J10"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="G13:H13"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="K10:L10"/>
+    <mergeCell ref="K9:L9"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M9:N9"/>
+    <mergeCell ref="K14:L14"/>
+    <mergeCell ref="K13:L13"/>
+    <mergeCell ref="K12:L12"/>
+    <mergeCell ref="K11:L11"/>
     <mergeCell ref="Q10:R10"/>
     <mergeCell ref="O11:P11"/>
     <mergeCell ref="O10:P10"/>
@@ -16894,62 +16628,20 @@
     <mergeCell ref="O8:P8"/>
     <mergeCell ref="Q8:R8"/>
     <mergeCell ref="Q9:R9"/>
-    <mergeCell ref="K10:L10"/>
-    <mergeCell ref="K9:L9"/>
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M10:N10"/>
-    <mergeCell ref="M9:N9"/>
-    <mergeCell ref="K14:L14"/>
-    <mergeCell ref="K13:L13"/>
-    <mergeCell ref="K12:L12"/>
-    <mergeCell ref="K11:L11"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="I13:J13"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="I10:J10"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="G13:H13"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="A4:R5"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C13:D13"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A20:A21"/>
-    <mergeCell ref="A22:A23"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A17:K17"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="C11:D11"/>
+    <mergeCell ref="A18:B19"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="Q13:R13"/>
+    <mergeCell ref="Q12:R12"/>
+    <mergeCell ref="Q11:R11"/>
+    <mergeCell ref="Q18:R18"/>
+    <mergeCell ref="O14:P14"/>
+    <mergeCell ref="O13:P13"/>
+    <mergeCell ref="O12:P12"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="K18:L18"/>
+    <mergeCell ref="M18:N18"/>
+    <mergeCell ref="O18:P18"/>
   </mergeCells>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" orientation="landscape" verticalDpi="0" r:id="rId1"/>
@@ -17003,29 +16695,29 @@
       <c r="A4" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="B4" s="129" t="s">
-        <v>370</v>
-      </c>
-      <c r="C4" s="129"/>
-      <c r="D4" s="129"/>
-      <c r="E4" s="129"/>
-      <c r="F4" s="129"/>
-      <c r="G4" s="129"/>
-      <c r="H4" s="129"/>
+      <c r="B4" s="148" t="s">
+        <v>369</v>
+      </c>
+      <c r="C4" s="148"/>
+      <c r="D4" s="148"/>
+      <c r="E4" s="148"/>
+      <c r="F4" s="148"/>
+      <c r="G4" s="148"/>
+      <c r="H4" s="148"/>
     </row>
     <row r="5" spans="1:14" ht="118" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="B5" s="130" t="s">
-        <v>369</v>
-      </c>
-      <c r="C5" s="130"/>
-      <c r="D5" s="130"/>
-      <c r="E5" s="130"/>
-      <c r="F5" s="130"/>
-      <c r="G5" s="130"/>
-      <c r="H5" s="130"/>
+      <c r="B5" s="149" t="s">
+        <v>472</v>
+      </c>
+      <c r="C5" s="149"/>
+      <c r="D5" s="149"/>
+      <c r="E5" s="149"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="149"/>
+      <c r="H5" s="149"/>
     </row>
     <row r="6" spans="1:14" s="7" customFormat="1" ht="25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="55" t="s">
@@ -17035,10 +16727,10 @@
         <v>367</v>
       </c>
       <c r="C6" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="D6" s="55" t="s">
         <v>393</v>
-      </c>
-      <c r="D6" s="55" t="s">
-        <v>394</v>
       </c>
       <c r="E6" s="55" t="s">
         <v>143</v>
@@ -19656,7 +19348,7 @@
     </row>
     <row r="4" spans="2:15" ht="26" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B4" s="67" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="C4" s="67"/>
       <c r="D4" s="67"/>
@@ -19690,7 +19382,7 @@
     </row>
     <row r="6" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B6" s="67" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="C6" s="67"/>
       <c r="D6" s="67"/>
@@ -19708,7 +19400,7 @@
     </row>
     <row r="7" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B7" s="68" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C7" s="68"/>
       <c r="D7" s="68"/>
@@ -19742,7 +19434,7 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B9" s="67" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="C9" s="67"/>
       <c r="D9" s="67"/>
@@ -19760,7 +19452,7 @@
     </row>
     <row r="10" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B10" s="68" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C10" s="68"/>
       <c r="D10" s="68"/>
@@ -19794,7 +19486,7 @@
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B12" s="67" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="C12" s="67"/>
       <c r="D12" s="67"/>
@@ -19812,7 +19504,7 @@
     </row>
     <row r="13" spans="2:15" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B13" s="68" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C13" s="68"/>
       <c r="D13" s="68"/>
@@ -19846,7 +19538,7 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B15" s="67" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C15" s="67"/>
       <c r="D15" s="67"/>
@@ -19864,7 +19556,7 @@
     </row>
     <row r="16" spans="2:15" ht="61" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B16" s="69" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="C16" s="70"/>
       <c r="D16" s="70"/>
@@ -19885,22 +19577,22 @@
         <v>132</v>
       </c>
       <c r="C17" s="71" t="s">
+        <v>402</v>
+      </c>
+      <c r="D17" s="71" t="s">
         <v>403</v>
       </c>
-      <c r="D17" s="71" t="s">
-        <v>404</v>
-      </c>
       <c r="E17" s="71" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="F17" s="72" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G17" s="72" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H17" s="72" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I17"/>
       <c r="J17"/>
@@ -19912,13 +19604,13 @@
     </row>
     <row r="18" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B18" s="73" t="s">
+        <v>404</v>
+      </c>
+      <c r="C18" s="73" t="s">
         <v>405</v>
       </c>
-      <c r="C18" s="73" t="s">
-        <v>406</v>
-      </c>
       <c r="D18" s="73" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="E18" s="74">
         <v>130</v>
@@ -19948,10 +19640,10 @@
         <v>283</v>
       </c>
       <c r="C19" s="76" t="s">
+        <v>406</v>
+      </c>
+      <c r="D19" s="76" t="s">
         <v>407</v>
-      </c>
-      <c r="D19" s="76" t="s">
-        <v>408</v>
       </c>
       <c r="E19" s="77">
         <v>40</v>
@@ -19978,13 +19670,13 @@
     </row>
     <row r="20" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B20" s="73" t="s">
+        <v>408</v>
+      </c>
+      <c r="C20" s="73" t="s">
+        <v>406</v>
+      </c>
+      <c r="D20" s="73" t="s">
         <v>409</v>
-      </c>
-      <c r="C20" s="73" t="s">
-        <v>407</v>
-      </c>
-      <c r="D20" s="73" t="s">
-        <v>410</v>
       </c>
       <c r="E20" s="79">
         <v>800</v>
@@ -20011,7 +19703,7 @@
     </row>
     <row r="21" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B21" s="80" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C21" s="80"/>
       <c r="D21" s="80"/>
@@ -20057,7 +19749,7 @@
     </row>
     <row r="23" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B23" s="67" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="C23" s="56"/>
       <c r="D23" s="56"/>
@@ -20075,7 +19767,7 @@
     </row>
     <row r="24" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B24" s="68" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C24"/>
       <c r="D24"/>
@@ -20093,7 +19785,7 @@
     </row>
     <row r="25" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B25" s="68" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C25"/>
       <c r="D25"/>
@@ -20111,7 +19803,7 @@
     </row>
     <row r="26" spans="2:15" x14ac:dyDescent="0.2">
       <c r="B26" s="68" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="C26"/>
       <c r="D26"/>
